--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30451-2025</t>
+          <t>A 22337-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45827</v>
+        <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,21 +1459,129 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Kransrams
+Myskmadra
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 30451-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bokstumpbagge
 Gråbandad trägnagare
@@ -1481,107 +1589,215 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Trollfibbla
+Kransrams
+Stor häxört
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 56294-2022</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>44887</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Crunoecia irrorata
 Skugglosta
@@ -1589,248 +1805,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 22337-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Kransrams
-Myskmadra
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Trollfibbla
-Kransrams
-Stor häxört
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45834</v>
+        <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,8 +2845,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2882,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2890,38 +2895,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2931,14 +2936,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45530</v>
+        <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2951,10 +2956,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>16.6</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2963,10 +2968,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2984,49 +2989,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3040,10 +3045,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45855</v>
+        <v>45530</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3056,22 +3061,22 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>16.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3089,49 +3094,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3141,14 +3146,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45204</v>
+        <v>45855</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3161,7 +3166,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3197,46 +3202,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3250,10 +3255,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44538</v>
+        <v>45471</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3281,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3290,58 +3295,62 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3351,14 +3360,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45189</v>
+        <v>45351</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3370,13 +3379,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3388,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3412,39 +3416,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
@@ -3468,7 +3472,7 @@
         <v>46169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3556,7 +3560,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3570,10 +3574,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45253</v>
+        <v>46043</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3586,82 +3590,82 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3675,10 +3679,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45471</v>
+        <v>44706</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3691,17 +3695,17 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3715,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3724,53 +3728,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3780,14 +3780,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46043</v>
+        <v>45189</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3799,8 +3799,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3812,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3836,46 +3841,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3889,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44706</v>
+        <v>45204</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3905,19 +3910,19 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3932,55 +3937,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3994,10 +3999,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45351</v>
+        <v>45183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4009,8 +4014,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4050,42 +4060,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4099,10 +4109,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45183</v>
+        <v>44538</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,13 +4124,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4132,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4153,49 +4158,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4209,10 +4214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45189</v>
+        <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4224,25 +4229,20 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4254,51 +4254,51 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44455</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44783</v>
+        <v>44886</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5050,14 +5050,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45713</v>
+        <v>44948</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45433</v>
+        <v>45265</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45433</v>
+        <v>45575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45265</v>
+        <v>45713</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45260</v>
+        <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44572</v>
+        <v>45645</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44886</v>
+        <v>45446</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5568,7 +5568,7 @@
         <v>45825</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45372</v>
+        <v>46029</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5653,8 +5653,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5697,7 +5702,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5711,10 +5716,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45152</v>
+        <v>46029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5726,8 +5731,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5770,7 +5780,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45827</v>
+        <v>44477</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5800,7 +5810,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5860,7 +5870,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5916,7 +5926,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5930,10 +5940,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46048</v>
+        <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5946,7 +5956,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5989,7 +5999,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6003,10 +6013,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45825</v>
+        <v>45827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6019,7 +6029,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6062,7 +6072,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6076,10 +6086,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45576</v>
+        <v>46043</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6092,7 +6102,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6135,7 +6145,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6149,10 +6159,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45845</v>
+        <v>45187</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6164,8 +6174,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6208,7 +6223,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6222,10 +6237,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45671</v>
+        <v>46049</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6237,8 +6252,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6281,7 +6301,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6291,14 +6311,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45848</v>
+        <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6311,7 +6331,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6354,7 +6374,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6368,10 +6388,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46008</v>
+        <v>46049</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6383,13 +6403,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6432,7 +6447,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6446,10 +6461,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>45845</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6462,7 +6477,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6505,7 +6520,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6515,14 +6530,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46008</v>
+        <v>46059</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6540,7 +6555,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6583,7 +6598,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6597,10 +6612,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45433</v>
+        <v>45029</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6613,7 +6628,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6656,7 +6671,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6673,7 +6688,7 @@
         <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6686,7 +6701,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6729,7 +6744,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6743,10 +6758,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45671</v>
+        <v>45576</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6759,7 +6774,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6802,7 +6817,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6816,10 +6831,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45014</v>
+        <v>45104</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6832,7 +6847,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6875,7 +6890,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6885,14 +6900,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45713</v>
+        <v>45848</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6905,7 +6920,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6948,7 +6963,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6962,10 +6977,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45940</v>
+        <v>46048</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6978,7 +6993,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7021,7 +7036,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7035,10 +7050,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46101</v>
+        <v>45671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7094,7 +7109,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7108,10 +7123,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46101</v>
+        <v>45671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7124,7 +7139,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7167,7 +7182,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7181,10 +7196,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45895</v>
+        <v>45189</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7196,8 +7211,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7240,7 +7260,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7254,10 +7274,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44477</v>
+        <v>46008</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7269,8 +7289,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7313,7 +7338,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7327,10 +7352,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7342,8 +7367,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7386,7 +7416,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7400,10 +7430,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45701</v>
+        <v>45940</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7416,7 +7446,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7459,7 +7489,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7473,10 +7503,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45799</v>
+        <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7488,8 +7518,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7532,7 +7567,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7546,10 +7581,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46029</v>
+        <v>44575</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7561,13 +7596,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>6.6</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7610,7 +7640,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7624,10 +7654,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46029</v>
+        <v>46101</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7637,11 +7667,6 @@
       <c r="G81" t="inlineStr">
         <is>
           <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -7688,7 +7713,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7702,10 +7727,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46043</v>
+        <v>45895</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7718,7 +7743,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7761,7 +7786,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7771,14 +7796,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45104</v>
+        <v>46101</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7791,7 +7816,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7834,7 +7859,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7848,10 +7873,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46049</v>
+        <v>44572</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7863,13 +7888,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7912,7 +7932,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7926,10 +7946,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46049</v>
+        <v>45471</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7942,7 +7962,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7985,7 +8005,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7995,14 +8015,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46059</v>
+        <v>45433</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8014,13 +8034,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8063,7 +8078,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8073,14 +8088,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46148</v>
+        <v>45433</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8093,7 +8108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8136,7 +8151,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8150,10 +8165,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45114</v>
+        <v>45799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8166,7 +8181,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8209,7 +8224,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8223,10 +8238,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44664</v>
+        <v>46001</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8239,7 +8254,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8282,7 +8297,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8292,14 +8307,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45407</v>
+        <v>45104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8312,7 +8327,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8355,7 +8370,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8365,14 +8380,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45140</v>
+        <v>45433</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8385,7 +8400,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8428,7 +8443,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8442,10 +8457,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44623</v>
+        <v>45259</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8458,7 +8473,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8501,7 +8516,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8515,10 +8530,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45433</v>
+        <v>44914</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8530,8 +8545,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8574,7 +8594,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8588,10 +8608,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45446</v>
+        <v>45260</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8604,7 +8624,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8647,7 +8667,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8657,14 +8677,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45187</v>
+        <v>46148</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8676,13 +8696,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8725,7 +8740,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8739,10 +8754,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45259</v>
+        <v>45666</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8755,7 +8770,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8798,7 +8813,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8812,10 +8827,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45905</v>
+        <v>45701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8828,7 +8843,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8871,7 +8886,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8885,10 +8900,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45191</v>
+        <v>45713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8901,7 +8916,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>9.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8944,7 +8959,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8954,14 +8969,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45217</v>
+        <v>45713</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8974,7 +8989,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9017,7 +9032,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9031,10 +9046,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45236</v>
+        <v>45385</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9048,11 +9063,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9095,7 +9110,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9109,10 +9124,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46184</v>
+        <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9125,7 +9140,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9168,7 +9183,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9182,10 +9197,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45471</v>
+        <v>46184</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9198,7 +9213,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9241,7 +9256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9251,14 +9266,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45163</v>
+        <v>44977</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9271,7 +9286,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9314,7 +9329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9324,14 +9339,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45385</v>
+        <v>45140</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,13 +9358,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9392,7 +9402,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9406,10 +9416,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44914</v>
+        <v>44713</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9421,13 +9431,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9470,7 +9475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9484,10 +9489,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45203</v>
+        <v>44600</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9500,7 +9505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9543,7 +9548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9557,10 +9562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45007</v>
+        <v>45372</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9573,7 +9578,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9616,7 +9621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9630,10 +9635,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44575</v>
+        <v>46211</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9645,8 +9650,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9689,7 +9699,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,10 +9713,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45282</v>
+        <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9719,7 +9729,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9762,7 +9772,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9776,10 +9786,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46211</v>
+        <v>45407</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9791,13 +9801,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9840,7 +9845,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9854,10 +9859,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45029</v>
+        <v>45407</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9870,7 +9875,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9913,7 +9918,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9927,10 +9932,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45104</v>
+        <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9986,7 +9991,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10000,10 +10005,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44600</v>
+        <v>45433</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10016,7 +10021,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10059,7 +10064,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10073,10 +10078,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45210</v>
+        <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10089,7 +10094,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10132,7 +10137,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10146,10 +10151,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45666</v>
+        <v>45191</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10162,7 +10167,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10222,7 +10227,7 @@
         <v>45163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10278,7 +10283,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10292,10 +10297,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44713</v>
+        <v>45152</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10308,7 +10313,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10351,7 +10356,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10365,10 +10370,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45189</v>
+        <v>45282</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10380,13 +10385,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10429,7 +10429,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45433</v>
+        <v>44664</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10502,7 +10502,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44977</v>
+        <v>45446</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10575,7 +10575,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10589,10 +10589,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45666</v>
+        <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10648,7 +10648,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45407</v>
+        <v>45114</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10721,7 +10721,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10735,10 +10735,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44948</v>
+        <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10750,8 +10750,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10794,7 +10799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10808,10 +10813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45446</v>
+        <v>45014</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10824,7 +10829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10867,7 +10872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10881,10 +10886,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44943</v>
+        <v>45666</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10897,7 +10902,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10940,7 +10945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10954,10 +10959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45090</v>
+        <v>45217</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10969,13 +10974,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45611</v>
+        <v>45210</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45784</v>
+        <v>45433</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45713</v>
+        <v>45007</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45576</v>
+        <v>45611</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11324,10 +11324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45575</v>
+        <v>45784</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45645</v>
+        <v>45713</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11456,7 +11456,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11470,10 +11470,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45713</v>
+        <v>45576</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11546,7 +11546,7 @@
         <v>44533</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46003</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>46059</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30451-2025</t>
+          <t>A 56294-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45827</v>
+        <v>44887</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,19 +1543,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1567,10 +1567,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1579,9 +1579,225 @@
         <v>4</v>
       </c>
       <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata
+Skugglosta
+Myskmadra
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Trollfibbla
+Kransrams
+Stor häxört
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 30451-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Bokstumpbagge
 Gråbandad trägnagare
@@ -1589,248 +1805,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Trollfibbla
-Kransrams
-Stor häxört
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 56294-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44887</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Crunoecia irrorata
-Skugglosta
-Myskmadra
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26736-2023</t>
+          <t>A 5166-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45090</v>
+        <v>46049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,20 +2196,25 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2224,164 +2229,159 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26736-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45090</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Månviol</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 5166-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45189</v>
+        <v>45253</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,25 +2845,20 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2875,58 +2870,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2935,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45834</v>
+        <v>45471</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,7 +2951,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2968,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2980,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2996,42 +2991,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3041,14 +3040,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45530</v>
+        <v>45204</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,10 +3060,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>16.6</v>
+        <v>6.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3073,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3094,49 +3093,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3146,14 +3145,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45855</v>
+        <v>46169</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,10 +3165,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3206,42 +3205,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,10 +3254,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45471</v>
+        <v>44706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,17 +3270,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3295,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3304,53 +3303,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45351</v>
+        <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3375,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3424,38 +3419,38 @@
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3469,10 +3464,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46169</v>
+        <v>44538</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3485,7 +3480,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3497,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3518,49 +3513,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3570,14 +3565,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46043</v>
+        <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3589,8 +3584,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3602,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3626,46 +3626,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44706</v>
+        <v>45351</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3704,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3722,55 +3722,55 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3780,14 +3780,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45189</v>
+        <v>45183</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3817,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3841,46 +3841,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45204</v>
+        <v>45189</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,8 +3909,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3954,38 +3959,38 @@
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3999,10 +4004,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45183</v>
+        <v>45834</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4014,16 +4019,11 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4056,46 +4056,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4105,14 +4105,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44538</v>
+        <v>45530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.2</v>
+        <v>16.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4158,49 +4158,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45253</v>
+        <v>45855</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,20 +4230,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4254,51 +4254,51 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21424-2022</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44706</v>
+        <v>45187</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4850,8 +4850,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4894,7 +4899,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50463-2021</t>
+          <t>A 21424-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4913,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44455</v>
+        <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4929,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4972,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44886</v>
+        <v>45259</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +5002,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5045,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 50463-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5050,14 +5055,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44948</v>
+        <v>44455</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5075,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5118,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45265</v>
+        <v>45191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5148,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5191,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5205,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45575</v>
+        <v>45433</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5221,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5264,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5278,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45713</v>
+        <v>45433</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5294,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5337,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5342,14 +5347,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44943</v>
+        <v>45217</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5362,7 +5367,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5405,7 +5410,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5424,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45645</v>
+        <v>44783</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5435,7 +5440,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5483,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5497,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45446</v>
+        <v>45236</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5507,8 +5512,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5561,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5565,10 +5575,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45825</v>
+        <v>45713</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5581,7 +5591,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5624,7 +5634,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5638,10 +5648,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46029</v>
+        <v>45265</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5653,13 +5663,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5702,7 +5707,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5716,10 +5721,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46029</v>
+        <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5731,13 +5736,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44477</v>
+        <v>45471</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45755</v>
+        <v>44572</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5943,7 +5943,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45827</v>
+        <v>44886</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46043</v>
+        <v>46101</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6145,7 +6145,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45187</v>
+        <v>46101</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6174,13 +6174,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6223,7 +6218,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46049</v>
+        <v>45671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6252,13 +6247,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6301,7 +6291,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6315,10 +6305,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45671</v>
+        <v>45163</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6331,7 +6321,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6374,7 +6364,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6388,10 +6378,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46049</v>
+        <v>45372</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6404,7 +6394,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6447,7 +6437,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6461,10 +6451,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45845</v>
+        <v>45152</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6477,7 +6467,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6520,7 +6510,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6530,14 +6520,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46059</v>
+        <v>45671</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6549,13 +6539,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6598,7 +6583,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6612,10 +6597,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45029</v>
+        <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6628,7 +6613,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6671,7 +6656,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6685,10 +6670,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45671</v>
+        <v>45940</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6701,7 +6686,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6744,7 +6729,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6758,10 +6743,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45576</v>
+        <v>45385</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6773,8 +6758,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6817,7 +6807,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6831,10 +6821,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45104</v>
+        <v>45576</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6847,7 +6837,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6890,7 +6880,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6900,14 +6890,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45848</v>
+        <v>45799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6920,7 +6910,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6963,7 +6953,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6977,10 +6967,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46048</v>
+        <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6993,7 +6983,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7036,7 +7026,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7050,10 +7040,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45671</v>
+        <v>45433</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7066,7 +7056,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7109,7 +7099,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7123,10 +7113,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45671</v>
+        <v>45014</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7139,7 +7129,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7182,7 +7172,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7196,10 +7186,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45189</v>
+        <v>45713</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7211,13 +7201,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7260,7 +7245,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7274,10 +7259,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46008</v>
+        <v>44914</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7291,11 +7276,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7338,7 +7323,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7352,10 +7337,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46008</v>
+        <v>45203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7367,13 +7352,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7416,7 +7396,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7426,14 +7406,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45940</v>
+        <v>46148</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7446,7 +7426,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7489,7 +7469,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7503,10 +7483,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45236</v>
+        <v>46001</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7518,13 +7498,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7567,7 +7542,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7581,10 +7556,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44575</v>
+        <v>44477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7597,7 +7572,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7640,7 +7615,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7654,10 +7629,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46101</v>
+        <v>46029</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7669,8 +7644,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7713,7 +7693,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7727,10 +7707,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45895</v>
+        <v>46029</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7742,8 +7722,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7786,7 +7771,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7800,10 +7785,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46101</v>
+        <v>45007</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7816,7 +7801,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7859,7 +7844,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7873,10 +7858,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44572</v>
+        <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7889,7 +7874,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7932,7 +7917,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7946,10 +7931,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45471</v>
+        <v>44575</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7962,7 +7947,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8005,7 +7990,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8019,10 +8004,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45433</v>
+        <v>46049</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8034,8 +8019,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8078,7 +8068,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8092,10 +8082,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45433</v>
+        <v>45282</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8108,7 +8098,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8151,7 +8141,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8165,10 +8155,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45799</v>
+        <v>45701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8181,7 +8171,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8224,7 +8214,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8238,10 +8228,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46001</v>
+        <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8254,7 +8244,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8297,7 +8287,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8307,14 +8297,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45104</v>
+        <v>46049</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8327,7 +8317,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8370,7 +8360,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8380,14 +8370,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45433</v>
+        <v>46059</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8399,8 +8389,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8443,7 +8438,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8457,10 +8452,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45259</v>
+        <v>46048</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8473,7 +8468,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8516,7 +8511,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44914</v>
+        <v>46184</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8545,13 +8540,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8594,7 +8584,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8608,10 +8598,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45260</v>
+        <v>46008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8623,8 +8613,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8667,7 +8662,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8677,14 +8672,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46148</v>
+        <v>45029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8697,7 +8692,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8740,7 +8735,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8754,10 +8749,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45666</v>
+        <v>46008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8769,8 +8764,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8813,7 +8813,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8823,14 +8823,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45701</v>
+        <v>45104</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8886,7 +8886,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8900,10 +8900,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45713</v>
+        <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8959,7 +8959,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45713</v>
+        <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9032,7 +9032,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45385</v>
+        <v>45210</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9061,13 +9061,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9110,7 +9105,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9124,10 +9119,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45905</v>
+        <v>45666</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9140,7 +9135,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>9.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9183,7 +9178,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9193,14 +9188,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46184</v>
+        <v>45163</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9213,7 +9208,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9256,7 +9251,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9266,14 +9261,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44977</v>
+        <v>45114</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9286,7 +9281,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9329,7 +9324,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9339,14 +9334,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45140</v>
+        <v>44664</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9359,7 +9354,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9402,7 +9397,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9416,10 +9411,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44713</v>
+        <v>46211</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9431,8 +9426,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44600</v>
+        <v>44713</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45372</v>
+        <v>45407</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9621,7 +9621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9631,14 +9631,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46211</v>
+        <v>45140</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9650,13 +9650,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9716,7 +9711,7 @@
         <v>44623</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9772,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9786,10 +9781,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45407</v>
+        <v>45189</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9801,8 +9796,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9845,7 +9845,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9859,10 +9859,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45407</v>
+        <v>45433</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9932,10 +9932,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45203</v>
+        <v>45446</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9991,7 +9991,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10008,7 +10008,7 @@
         <v>45433</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10074,14 +10074,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44783</v>
+        <v>44977</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45191</v>
+        <v>45666</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>9.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10210,7 +10210,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10220,14 +10220,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45163</v>
+        <v>45407</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>9.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10283,7 +10283,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10293,14 +10293,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45152</v>
+        <v>44948</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10356,7 +10356,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10370,10 +10370,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45282</v>
+        <v>45446</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10429,7 +10429,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44664</v>
+        <v>44943</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10502,7 +10502,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10512,14 +10512,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45446</v>
+        <v>45090</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10531,8 +10531,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10575,7 +10580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10589,10 +10594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45163</v>
+        <v>45611</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10605,7 +10610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10648,7 +10653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10662,10 +10667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45114</v>
+        <v>45784</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10678,7 +10683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10721,7 +10726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10731,14 +10736,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45090</v>
+        <v>45713</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10750,13 +10755,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10799,7 +10799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45014</v>
+        <v>45576</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10872,7 +10872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45666</v>
+        <v>45575</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10955,14 +10955,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45217</v>
+        <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45210</v>
+        <v>45713</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45433</v>
+        <v>45825</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45007</v>
+        <v>45827</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45611</v>
+        <v>45755</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11324,10 +11324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45784</v>
+        <v>45845</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45713</v>
+        <v>45671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11456,7 +11456,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11466,14 +11466,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45576</v>
+        <v>45848</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11546,7 +11546,7 @@
         <v>44533</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46003</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>46059</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE136"/>
+  <dimension ref="A1:AE135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 56294-2022</t>
+          <t>A 30451-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44887</v>
+        <v>45827</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1543,19 +1543,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1567,10 +1567,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1579,9 +1579,225 @@
         <v>4</v>
       </c>
       <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Bokstumpbagge
+Gråbandad trägnagare
+Skogsveronika
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Trollfibbla
+Kransrams
+Stor häxört
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 56294-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44887</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Crunoecia irrorata
 Skugglosta
@@ -1589,248 +1805,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Trollfibbla
-Kransrams
-Stor häxört
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30451-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45827</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Bokstumpbagge
-Gråbandad trägnagare
-Skogsveronika
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5166-2026</t>
+          <t>A 26736-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46049</v>
+        <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,25 +2196,20 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2229,159 +2224,164 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Månviol</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5166-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Entita
 Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26736-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45090</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Månviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45253</v>
+        <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,21 +2845,26 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2870,58 +2875,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2935,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45471</v>
+        <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2951,7 +2956,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2963,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2975,10 +2980,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2991,46 +2996,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3040,14 +3041,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45204</v>
+        <v>45530</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,22 +3061,22 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.1</v>
+        <v>16.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3093,49 +3094,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3145,14 +3146,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46169</v>
+        <v>45855</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3165,10 +3166,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3205,42 +3206,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3254,10 +3255,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44706</v>
+        <v>45471</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3270,16 +3271,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3294,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3303,49 +3304,53 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46043</v>
+        <v>45351</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3375,7 +3380,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3419,38 +3424,38 @@
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3464,10 +3469,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44538</v>
+        <v>44706</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3480,7 +3485,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3489,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3507,48 +3512,48 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
@@ -3572,7 +3577,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3665,7 +3670,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3679,10 +3684,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45351</v>
+        <v>45204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3695,10 +3700,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3735,42 +3740,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45183</v>
+        <v>46043</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3799,13 +3804,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3845,42 +3845,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45189</v>
+        <v>45183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3955,42 +3955,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45834</v>
+        <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4020,22 +4020,22 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4053,49 +4053,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4105,14 +4105,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45530</v>
+        <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4125,13 +4125,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>16.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4149,58 +4149,58 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45855</v>
+        <v>46169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4270,35 +4270,35 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 21424-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45187</v>
+        <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4850,13 +4850,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4899,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21424-2022</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4913,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44706</v>
+        <v>44886</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4929,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4972,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4982,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45259</v>
+        <v>44948</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5002,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5045,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50463-2021</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5059,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44455</v>
+        <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5075,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5118,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45191</v>
+        <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5148,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5191,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5205,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45433</v>
+        <v>44477</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5221,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5264,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5278,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45433</v>
+        <v>45575</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5294,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5337,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5347,14 +5342,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45217</v>
+        <v>45446</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5367,7 +5362,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5410,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5424,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44783</v>
+        <v>45713</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5440,7 +5435,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5483,7 +5478,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5497,10 +5492,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45236</v>
+        <v>45645</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5512,13 +5507,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5561,7 +5551,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5575,10 +5565,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45713</v>
+        <v>46029</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5590,8 +5580,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5634,7 +5629,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45265</v>
+        <v>46029</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5663,8 +5658,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45260</v>
+        <v>45187</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5734,6 +5734,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5780,7 +5785,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5794,10 +5799,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45471</v>
+        <v>45825</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5810,7 +5815,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5853,7 +5858,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5867,10 +5872,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44572</v>
+        <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5883,7 +5888,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5926,7 +5931,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5943,7 +5948,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5956,7 +5961,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5999,7 +6004,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6013,10 +6018,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44886</v>
+        <v>45827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6072,7 +6077,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6086,10 +6091,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46101</v>
+        <v>45029</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6102,7 +6107,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6145,7 +6150,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6159,10 +6164,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46101</v>
+        <v>45576</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6175,7 +6180,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6218,7 +6223,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6232,10 +6237,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45671</v>
+        <v>45104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6248,7 +6253,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6291,7 +6296,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45163</v>
+        <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6321,7 +6326,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6364,7 +6369,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6378,10 +6383,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45372</v>
+        <v>45189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6393,8 +6398,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6437,7 +6447,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6451,10 +6461,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45152</v>
+        <v>45845</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6467,7 +6477,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6510,7 +6520,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6524,10 +6534,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45671</v>
+        <v>45236</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6539,8 +6549,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6583,7 +6598,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6600,7 +6615,7 @@
         <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6613,7 +6628,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6656,7 +6671,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6670,10 +6685,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45940</v>
+        <v>44575</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6686,7 +6701,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6729,7 +6744,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6739,14 +6754,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45385</v>
+        <v>45848</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6758,13 +6773,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6807,7 +6817,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6821,10 +6831,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45576</v>
+        <v>45671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6837,7 +6847,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6880,7 +6890,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6894,10 +6904,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45799</v>
+        <v>45671</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6910,7 +6920,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6953,7 +6963,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6967,10 +6977,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45895</v>
+        <v>46043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6983,7 +6993,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7026,7 +7036,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7040,10 +7050,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45433</v>
+        <v>45940</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7056,7 +7066,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7099,7 +7109,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7113,10 +7123,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45014</v>
+        <v>46049</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7128,8 +7138,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7172,7 +7187,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7186,10 +7201,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45713</v>
+        <v>46049</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7202,7 +7217,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7245,7 +7260,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7259,10 +7274,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44914</v>
+        <v>45895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7274,13 +7289,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7323,7 +7333,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7337,10 +7347,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45203</v>
+        <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7353,7 +7363,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7396,7 +7406,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7406,14 +7416,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46148</v>
+        <v>46059</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7425,8 +7435,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7469,7 +7484,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7483,10 +7498,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46001</v>
+        <v>45471</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7499,7 +7514,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7542,7 +7557,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7556,10 +7571,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44477</v>
+        <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7572,7 +7587,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7615,7 +7630,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7629,10 +7644,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46029</v>
+        <v>45433</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7644,13 +7659,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7693,7 +7703,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7707,10 +7717,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46029</v>
+        <v>45433</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7722,13 +7732,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7771,7 +7776,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7785,10 +7790,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45007</v>
+        <v>46008</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7800,8 +7805,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7844,7 +7854,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7858,10 +7868,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46043</v>
+        <v>46008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7873,8 +7883,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7917,7 +7932,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7927,14 +7942,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44575</v>
+        <v>45104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7990,7 +8005,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8004,10 +8019,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46049</v>
+        <v>46001</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8019,13 +8034,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8068,7 +8078,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8082,10 +8092,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45282</v>
+        <v>45433</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8098,7 +8108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8141,7 +8151,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8155,10 +8165,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45701</v>
+        <v>45259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8214,7 +8224,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8228,10 +8238,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45905</v>
+        <v>44914</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8243,8 +8253,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>9.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8287,7 +8302,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8301,10 +8316,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46049</v>
+        <v>45260</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8317,7 +8332,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8360,7 +8375,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8370,14 +8385,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46059</v>
+        <v>46101</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8389,13 +8404,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8438,7 +8448,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8452,10 +8462,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46048</v>
+        <v>46101</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8468,7 +8478,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8511,7 +8521,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8525,10 +8535,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46184</v>
+        <v>45666</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8541,7 +8551,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8584,7 +8594,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8598,10 +8608,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46008</v>
+        <v>45701</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8613,13 +8623,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8662,7 +8667,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8676,10 +8681,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45029</v>
+        <v>45713</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8692,7 +8697,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8735,7 +8740,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8749,10 +8754,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46008</v>
+        <v>45713</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8764,13 +8769,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8813,7 +8813,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8823,14 +8823,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45104</v>
+        <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8842,8 +8842,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8886,7 +8891,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8896,14 +8901,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45104</v>
+        <v>44977</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8916,7 +8921,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8959,7 +8964,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8969,14 +8974,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44600</v>
+        <v>45140</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8989,7 +8994,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9032,7 +9037,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45210</v>
+        <v>44713</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9062,7 +9067,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9105,7 +9110,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9119,10 +9124,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45666</v>
+        <v>44600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9135,7 +9140,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9178,7 +9183,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9188,14 +9193,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45163</v>
+        <v>45372</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9208,7 +9213,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9251,7 +9256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9265,10 +9270,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45114</v>
+        <v>44623</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9281,7 +9286,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9324,7 +9329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9338,10 +9343,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44664</v>
+        <v>45799</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9354,7 +9359,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9397,7 +9402,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9411,10 +9416,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46211</v>
+        <v>45407</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9426,13 +9431,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44713</v>
+        <v>45407</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45407</v>
+        <v>45203</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9621,7 +9621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9635,10 +9635,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45140</v>
+        <v>46148</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44623</v>
+        <v>45433</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45189</v>
+        <v>44783</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9796,13 +9796,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9845,7 +9840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9859,10 +9854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45433</v>
+        <v>45191</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9875,7 +9870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9918,7 +9913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9928,14 +9923,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45446</v>
+        <v>45163</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9948,7 +9943,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9991,7 +9986,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10005,10 +10000,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45433</v>
+        <v>45152</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10021,7 +10016,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10064,7 +10059,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10074,14 +10069,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44977</v>
+        <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10094,7 +10089,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10137,7 +10132,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10151,10 +10146,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45666</v>
+        <v>44664</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10167,7 +10162,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10210,7 +10205,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10224,10 +10219,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45407</v>
+        <v>45446</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10240,7 +10235,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10283,7 +10278,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10293,14 +10288,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44948</v>
+        <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10313,7 +10308,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10356,7 +10351,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10370,10 +10365,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45446</v>
+        <v>45114</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10386,7 +10381,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10429,7 +10424,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10443,10 +10438,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44943</v>
+        <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10459,7 +10454,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10502,7 +10497,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10512,14 +10507,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45090</v>
+        <v>46184</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10531,13 +10526,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10580,7 +10570,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10590,14 +10580,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45611</v>
+        <v>45090</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10609,8 +10599,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10653,7 +10648,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10667,10 +10662,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45784</v>
+        <v>45014</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10683,7 +10678,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10726,7 +10721,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10740,10 +10735,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45713</v>
+        <v>45666</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10756,7 +10751,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10799,7 +10794,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10809,14 +10804,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45576</v>
+        <v>45217</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10829,7 +10824,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10872,7 +10867,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10886,10 +10881,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45575</v>
+        <v>46211</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10901,8 +10896,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45645</v>
+        <v>45210</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45713</v>
+        <v>45433</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45825</v>
+        <v>45007</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45827</v>
+        <v>45611</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45755</v>
+        <v>45784</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11324,10 +11324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45845</v>
+        <v>45713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45671</v>
+        <v>45576</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11456,24 +11456,24 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>S 9900-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45848</v>
+        <v>44533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.1</v>
+        <v>28.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11529,7 +11529,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S 9900-2021</t>
+          <t>S 3504-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11539,14 +11539,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44533</v>
+        <v>46003</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>28.1</v>
+        <v>0.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11599,10 +11599,10 @@
       </c>
       <c r="V134" s="2" t="inlineStr"/>
     </row>
-    <row r="135" ht="15" customHeight="1">
+    <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S 3504-2025</t>
+          <t>S 307-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11616,10 +11616,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46003</v>
+        <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11631,8 +11631,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11671,84 +11676,6 @@
         <v>0</v>
       </c>
       <c r="V135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>S 307-2026</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D136" s="1" t="n">
-        <v>46059</v>
-      </c>
-      <c r="E136" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I136" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 22337-2024</t>
+          <t>A 30451-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45446</v>
+        <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,21 +1459,237 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bokstumpbagge
+Gråbandad trägnagare
+Skogsveronika
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 56294-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44887</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata
+Skugglosta
+Myskmadra
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 22337-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Kransrams
@@ -1481,215 +1697,107 @@
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 30451-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>45827</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="D12" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bokstumpbagge
-Gråbandad trägnagare
-Skogsveronika
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trollfibbla
 Kransrams
@@ -1697,140 +1805,32 @@
 Tvåblad</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 56294-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44887</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Crunoecia irrorata
-Skugglosta
-Myskmadra
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45189</v>
+        <v>45834</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,13 +2845,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2887,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -2895,38 +2890,38 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2936,14 +2931,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45834</v>
+        <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,22 +2951,22 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>16.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2989,49 +2984,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3045,10 +3040,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45530</v>
+        <v>45855</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,10 +3056,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>16.6</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3073,10 +3068,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3094,49 +3089,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3146,14 +3141,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45855</v>
+        <v>45204</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,7 +3161,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3202,46 +3197,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,10 +3250,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45471</v>
+        <v>44538</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,23 +3266,23 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -3295,62 +3290,58 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3364,10 +3355,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45351</v>
+        <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3371,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3424,38 +3415,38 @@
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3465,14 +3456,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44706</v>
+        <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3484,8 +3475,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3494,13 +3490,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3512,55 +3508,55 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3570,14 +3566,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45189</v>
+        <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3589,19 +3585,14 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3610,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3619,58 +3610,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3684,10 +3675,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45204</v>
+        <v>45471</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3700,7 +3691,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3712,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3724,10 +3715,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3736,46 +3727,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46043</v>
+        <v>46169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3805,7 +3800,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3841,46 +3836,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3889,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45183</v>
+        <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,13 +3904,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3924,10 +3914,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3942,55 +3932,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4004,10 +3994,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44538</v>
+        <v>45351</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4020,7 +4010,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4032,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4053,49 +4043,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4109,10 +4099,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45253</v>
+        <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4124,83 +4114,88 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4214,10 +4209,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46169</v>
+        <v>45189</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4229,11 +4224,16 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4266,39 +4266,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44886</v>
+        <v>44783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44948</v>
+        <v>45713</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45265</v>
+        <v>45433</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44943</v>
+        <v>45433</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44477</v>
+        <v>45265</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45575</v>
+        <v>45260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45446</v>
+        <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45713</v>
+        <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45645</v>
+        <v>45825</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46029</v>
+        <v>46048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5580,13 +5580,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5629,7 +5624,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5643,10 +5638,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46029</v>
+        <v>45372</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5658,13 +5653,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5707,7 +5697,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5721,10 +5711,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45187</v>
+        <v>45152</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5736,13 +5726,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5785,7 +5770,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5799,10 +5784,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45825</v>
+        <v>45827</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5815,7 +5800,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5875,7 +5860,7 @@
         <v>45755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5931,7 +5916,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5945,10 +5930,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45825</v>
+        <v>46008</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5960,8 +5945,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6004,7 +5994,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6018,10 +6008,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45827</v>
+        <v>46008</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6033,8 +6023,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6077,7 +6072,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6091,10 +6086,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45029</v>
+        <v>45576</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6107,7 +6102,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6150,7 +6145,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6164,10 +6159,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45576</v>
+        <v>45825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6180,7 +6175,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6223,7 +6218,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45104</v>
+        <v>45845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6253,7 +6248,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6296,7 +6291,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45671</v>
+        <v>46101</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6326,7 +6321,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6369,7 +6364,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6383,10 +6378,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45189</v>
+        <v>46101</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6398,13 +6393,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6447,7 +6437,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6461,10 +6451,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45845</v>
+        <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6477,7 +6467,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6520,7 +6510,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6530,14 +6520,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45236</v>
+        <v>45848</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6549,13 +6539,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6598,7 +6583,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6612,10 +6597,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45671</v>
+        <v>45433</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6628,7 +6613,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6671,7 +6656,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6685,10 +6670,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44575</v>
+        <v>45014</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6701,7 +6686,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6744,7 +6729,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6754,14 +6739,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45848</v>
+        <v>45713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6774,7 +6759,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6817,7 +6802,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6831,10 +6816,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45671</v>
+        <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6847,7 +6832,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6890,7 +6875,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6907,7 +6892,7 @@
         <v>45671</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6920,7 +6905,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6963,7 +6948,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6977,10 +6962,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46043</v>
+        <v>44477</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6993,7 +6978,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7036,7 +7021,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7050,10 +7035,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45940</v>
+        <v>45671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7066,7 +7051,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7109,7 +7094,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7123,10 +7108,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46049</v>
+        <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7138,13 +7123,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7187,7 +7167,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7197,14 +7177,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46049</v>
+        <v>46148</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7217,7 +7197,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7260,7 +7240,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7274,10 +7254,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45895</v>
+        <v>45671</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7290,7 +7270,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7333,7 +7313,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7347,10 +7327,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44572</v>
+        <v>45940</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7363,7 +7343,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7406,7 +7386,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7416,14 +7396,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46059</v>
+        <v>45104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7435,13 +7415,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7484,7 +7459,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7498,10 +7473,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45471</v>
+        <v>45905</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7514,7 +7489,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7557,7 +7532,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7571,10 +7546,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46048</v>
+        <v>45895</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7587,7 +7562,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7630,7 +7605,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7644,10 +7619,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45433</v>
+        <v>46184</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7660,7 +7635,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7703,7 +7678,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7717,10 +7692,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45433</v>
+        <v>45114</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7733,7 +7708,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7776,7 +7751,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7790,10 +7765,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46008</v>
+        <v>44664</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7805,13 +7780,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7854,7 +7824,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7868,10 +7838,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46008</v>
+        <v>45407</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7883,13 +7853,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7932,7 +7897,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7946,10 +7911,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45104</v>
+        <v>45140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7962,7 +7927,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8005,7 +7970,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8019,10 +7984,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46001</v>
+        <v>44623</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8035,7 +8000,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8095,7 +8060,7 @@
         <v>45433</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8151,7 +8116,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8165,10 +8130,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45259</v>
+        <v>45446</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8181,7 +8146,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8224,7 +8189,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8238,10 +8203,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44914</v>
+        <v>45187</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8255,11 +8220,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8302,7 +8267,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8316,10 +8281,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45260</v>
+        <v>45259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8332,7 +8297,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8375,7 +8340,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8389,10 +8354,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46101</v>
+        <v>46211</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8404,8 +8369,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8448,7 +8418,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8462,10 +8432,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46101</v>
+        <v>45191</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8478,7 +8448,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8521,7 +8491,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8531,14 +8501,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45666</v>
+        <v>45217</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8551,7 +8521,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8594,7 +8564,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8608,10 +8578,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45701</v>
+        <v>45236</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8623,8 +8593,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8667,7 +8642,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8681,10 +8656,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45713</v>
+        <v>46001</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8697,7 +8672,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8740,7 +8715,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8754,10 +8729,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45713</v>
+        <v>45471</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8813,7 +8788,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8827,10 +8802,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45385</v>
+        <v>45163</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8842,13 +8817,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8891,7 +8861,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8901,14 +8871,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44977</v>
+        <v>45385</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8920,8 +8890,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8964,7 +8939,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8974,14 +8949,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45140</v>
+        <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8993,8 +8968,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9037,7 +9017,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9051,10 +9031,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44713</v>
+        <v>46029</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9066,8 +9046,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9110,7 +9095,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9124,10 +9109,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44600</v>
+        <v>44914</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9139,8 +9124,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9183,7 +9173,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9197,10 +9187,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45372</v>
+        <v>45203</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9213,7 +9203,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9256,7 +9246,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9270,10 +9260,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44623</v>
+        <v>45007</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9286,7 +9276,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9329,7 +9319,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9343,10 +9333,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45799</v>
+        <v>44575</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9359,7 +9349,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9402,7 +9392,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9416,10 +9406,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45407</v>
+        <v>45282</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9432,7 +9422,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9475,7 +9465,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9489,10 +9479,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45407</v>
+        <v>46043</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9505,7 +9495,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9548,7 +9538,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9562,10 +9552,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45203</v>
+        <v>45029</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9578,7 +9568,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9621,7 +9611,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9631,14 +9621,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46148</v>
+        <v>46049</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9650,8 +9640,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9689,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9708,10 +9703,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45433</v>
+        <v>45104</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9724,7 +9719,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.5</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9762,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9781,10 +9776,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44783</v>
+        <v>44600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9797,7 +9792,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9840,7 +9835,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9854,10 +9849,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45191</v>
+        <v>46049</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9870,7 +9865,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>9.300000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9913,7 +9908,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9923,14 +9918,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45163</v>
+        <v>45210</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9943,7 +9938,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>9.300000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9986,7 +9981,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10000,10 +9995,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45152</v>
+        <v>45666</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10016,7 +10011,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10059,7 +10054,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10069,14 +10064,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45282</v>
+        <v>45163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10089,7 +10084,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10132,7 +10127,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10142,14 +10137,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44664</v>
+        <v>46059</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10159,6 +10154,11 @@
       <c r="G115" t="inlineStr">
         <is>
           <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -10205,7 +10205,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45446</v>
+        <v>44713</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45163</v>
+        <v>45189</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10307,8 +10307,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10351,7 +10356,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10365,10 +10370,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45114</v>
+        <v>45433</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10381,7 +10386,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10424,7 +10429,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10434,14 +10439,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45905</v>
+        <v>44977</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10454,7 +10459,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>9.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10497,7 +10502,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10511,10 +10516,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46184</v>
+        <v>45666</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10527,7 +10532,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10570,7 +10575,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10580,14 +10585,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45090</v>
+        <v>45407</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10599,13 +10604,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10648,7 +10648,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10658,14 +10658,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45014</v>
+        <v>44948</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10721,7 +10721,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10735,10 +10735,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45666</v>
+        <v>45446</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10804,14 +10804,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45217</v>
+        <v>44943</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10877,14 +10877,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46211</v>
+        <v>45090</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10898,11 +10898,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45210</v>
+        <v>45611</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45433</v>
+        <v>45784</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45007</v>
+        <v>45713</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45611</v>
+        <v>45576</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45784</v>
+        <v>45575</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11324,10 +11324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45713</v>
+        <v>45645</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45576</v>
+        <v>45713</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11473,7 +11473,7 @@
         <v>44533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>46003</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30451-2025</t>
+          <t>A 22337-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45827</v>
+        <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,21 +1459,345 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Kransrams
+Myskmadra
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Trollfibbla
+Kransrams
+Stor häxört
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 56294-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44887</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata
+Skugglosta
+Myskmadra
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 30451-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Bokstumpbagge
 Gråbandad trägnagare
@@ -1481,356 +1805,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 56294-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44887</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Crunoecia irrorata
-Skugglosta
-Myskmadra
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 22337-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Kransrams
-Myskmadra
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Trollfibbla
-Kransrams
-Stor häxört
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 5166-2026</t>
+          <t>A 16340-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46049</v>
+        <v>45407</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2302,22 +2302,17 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2332,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2344,150 +2339,155 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 16340-2024 artfynd.xlsx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 16340-2024 karta.png", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 16340-2024 georefererad karta.tif", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 16340-2024 FSC-klagomål.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 16340-2024 FSC-klagomål mail.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 16340-2024 tillsynsbegäran.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 16340-2024 tillsynsbegäran mail.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5166-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Entita
 Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 16340-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45407</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 16340-2024 artfynd.xlsx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 16340-2024 karta.png", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 16340-2024 georefererad karta.tif", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 16340-2024 FSC-klagomål.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 16340-2024 FSC-klagomål mail.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 16340-2024 tillsynsbegäran.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 16340-2024 tillsynsbegäran mail.docx", "A 16340-2024")</f>
         <v/>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45834</v>
+        <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2870,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2886,42 +2886,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2931,14 +2935,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45530</v>
+        <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2951,7 +2955,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>16.6</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2963,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2984,49 +2988,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3036,14 +3040,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45855</v>
+        <v>44706</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3056,19 +3060,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3083,55 +3087,55 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3141,14 +3145,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45204</v>
+        <v>45189</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3160,23 +3164,28 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3197,46 +3206,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3250,10 +3259,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44538</v>
+        <v>45204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3266,10 +3275,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3278,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3299,42 +3308,42 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
@@ -3358,7 +3367,7 @@
         <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3446,7 +3455,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3456,14 +3465,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>45183</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3477,11 +3486,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3493,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3517,46 +3526,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3570,10 +3579,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45253</v>
+        <v>44538</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3586,82 +3595,82 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3675,10 +3684,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45471</v>
+        <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3691,13 +3700,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3724,46 +3733,42 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
@@ -3787,7 +3792,7 @@
         <v>46169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3875,7 +3880,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3889,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44706</v>
+        <v>45189</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3904,20 +3909,25 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3932,55 +3942,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3994,10 +4004,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45351</v>
+        <v>45834</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4010,10 +4020,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4046,46 +4056,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4095,14 +4105,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45183</v>
+        <v>45530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,13 +4124,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>16.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4132,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4153,49 +4158,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4205,14 +4210,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45189</v>
+        <v>45855</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4224,13 +4229,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4266,39 +4266,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44783</v>
+        <v>44886</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45713</v>
+        <v>45265</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5050,14 +5050,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45433</v>
+        <v>44948</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45433</v>
+        <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45265</v>
+        <v>45446</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45260</v>
+        <v>44477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44572</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5361,8 +5361,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5405,7 +5410,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5424,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44886</v>
+        <v>45576</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5435,7 +5440,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5483,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5497,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45825</v>
+        <v>45029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5508,7 +5513,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5556,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5565,10 +5570,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46048</v>
+        <v>45104</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5581,7 +5586,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5624,7 +5629,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5638,10 +5643,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45372</v>
+        <v>45189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5653,8 +5658,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5697,7 +5707,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5711,10 +5721,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45152</v>
+        <v>45236</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5726,8 +5736,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5770,7 +5785,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5784,10 +5799,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45827</v>
+        <v>44575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5800,7 +5815,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5843,7 +5858,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5857,10 +5872,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45755</v>
+        <v>44572</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5873,7 +5888,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5916,7 +5931,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5930,10 +5945,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46008</v>
+        <v>45471</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5945,13 +5960,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5994,7 +6004,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6008,10 +6018,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46008</v>
+        <v>45433</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6023,13 +6033,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6072,7 +6077,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6086,10 +6091,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45576</v>
+        <v>45433</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6102,7 +6107,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6162,7 +6167,7 @@
         <v>45825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6218,7 +6223,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6232,10 +6237,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45845</v>
+        <v>45799</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6248,7 +6253,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6291,7 +6296,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6301,14 +6306,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46101</v>
+        <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6321,7 +6326,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6364,7 +6369,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6378,10 +6383,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46101</v>
+        <v>45433</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6394,7 +6399,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6437,7 +6442,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6451,10 +6456,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>45259</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6467,7 +6472,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6510,7 +6515,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6520,14 +6525,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45848</v>
+        <v>44914</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6539,8 +6544,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6583,7 +6593,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6597,10 +6607,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45433</v>
+        <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6613,7 +6623,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6656,7 +6666,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6670,10 +6680,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45014</v>
+        <v>45260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6686,7 +6696,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6729,7 +6739,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6743,10 +6753,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45713</v>
+        <v>45671</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6759,7 +6769,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6802,7 +6812,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6816,10 +6826,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45799</v>
+        <v>45671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6832,7 +6842,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6875,7 +6885,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6889,10 +6899,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45671</v>
+        <v>45666</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6905,7 +6915,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6948,7 +6958,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6962,10 +6972,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44477</v>
+        <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6978,7 +6988,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7021,7 +7031,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7031,14 +7041,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45671</v>
+        <v>46148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7051,7 +7061,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7094,7 +7104,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7108,10 +7118,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45701</v>
+        <v>45940</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7124,7 +7134,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7167,7 +7177,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7177,14 +7187,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46148</v>
+        <v>45713</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7197,7 +7207,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7240,7 +7250,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7254,10 +7264,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45671</v>
+        <v>45713</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7270,7 +7280,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7313,7 +7323,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7327,10 +7337,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45940</v>
+        <v>45385</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7342,8 +7352,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7386,7 +7401,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7400,10 +7415,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45104</v>
+        <v>44977</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7416,7 +7431,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7459,7 +7474,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7473,10 +7488,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45905</v>
+        <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7489,7 +7504,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7532,7 +7547,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7542,14 +7557,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45895</v>
+        <v>45140</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7562,7 +7577,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7605,7 +7620,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7619,10 +7634,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46184</v>
+        <v>44713</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7635,7 +7650,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7678,7 +7693,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7692,10 +7707,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45114</v>
+        <v>44600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7708,7 +7723,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7751,7 +7766,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7765,10 +7780,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44664</v>
+        <v>45372</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7824,7 +7839,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7838,10 +7853,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45407</v>
+        <v>44623</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7854,7 +7869,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7897,7 +7912,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7907,14 +7922,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45140</v>
+        <v>45407</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7927,7 +7942,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7970,7 +7985,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7984,10 +7999,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44623</v>
+        <v>45407</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8000,7 +8015,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8043,7 +8058,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8057,10 +8072,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45433</v>
+        <v>45203</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8073,7 +8088,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8116,7 +8131,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8130,10 +8145,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45446</v>
+        <v>46001</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8146,7 +8161,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8189,7 +8204,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8203,10 +8218,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45187</v>
+        <v>45433</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8218,13 +8233,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8267,7 +8277,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8281,10 +8291,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45259</v>
+        <v>44783</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8297,7 +8307,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8340,7 +8350,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46211</v>
+        <v>45191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8369,13 +8379,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>4.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8418,7 +8423,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8432,10 +8437,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45191</v>
+        <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8447,8 +8452,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>9.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8491,7 +8501,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8501,14 +8511,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45217</v>
+        <v>46029</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8520,8 +8530,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8564,7 +8579,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8574,14 +8589,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45236</v>
+        <v>45163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8593,13 +8608,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>5.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8642,7 +8652,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8656,10 +8666,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46001</v>
+        <v>45152</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8672,7 +8682,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8715,7 +8725,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8729,10 +8739,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45471</v>
+        <v>45282</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8745,7 +8755,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8788,7 +8798,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8802,10 +8812,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45163</v>
+        <v>46043</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8818,7 +8828,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8861,7 +8871,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8875,10 +8885,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45385</v>
+        <v>46049</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8896,7 +8906,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8939,7 +8949,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8953,10 +8963,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46029</v>
+        <v>44664</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8968,13 +8978,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9017,7 +9022,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9031,10 +9036,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46029</v>
+        <v>46049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9046,13 +9051,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44914</v>
+        <v>45446</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9124,13 +9124,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9173,7 +9168,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9187,10 +9182,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45203</v>
+        <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9203,7 +9198,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9246,7 +9241,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9260,10 +9255,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45007</v>
+        <v>45163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9276,7 +9271,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9319,7 +9314,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9329,14 +9324,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44575</v>
+        <v>46059</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9348,8 +9343,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9392,7 +9392,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9406,10 +9406,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45282</v>
+        <v>46048</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9465,7 +9465,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46043</v>
+        <v>45114</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9538,7 +9538,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45029</v>
+        <v>46008</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9567,8 +9567,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9611,7 +9616,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9625,10 +9630,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46049</v>
+        <v>46008</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9642,11 +9647,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9689,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,10 +9708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45104</v>
+        <v>46184</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9719,7 +9724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9762,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9772,14 +9777,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44600</v>
+        <v>45090</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9791,8 +9796,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9835,7 +9845,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9849,10 +9859,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46049</v>
+        <v>46101</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9865,7 +9875,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9908,7 +9918,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9922,10 +9932,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45210</v>
+        <v>46101</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9938,7 +9948,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9981,7 +9991,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9995,10 +10005,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45666</v>
+        <v>45014</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10011,7 +10021,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10054,7 +10064,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10064,14 +10074,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45163</v>
+        <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10084,7 +10094,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>9.300000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10127,7 +10137,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10137,14 +10147,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46059</v>
+        <v>45217</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10156,13 +10166,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10205,7 +10210,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10219,10 +10224,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44713</v>
+        <v>45210</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10235,7 +10240,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10278,7 +10283,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10292,10 +10297,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45189</v>
+        <v>46211</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10309,11 +10314,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10373,7 +10378,7 @@
         <v>45433</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10429,7 +10434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10439,14 +10444,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44977</v>
+        <v>45007</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10459,7 +10464,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10502,7 +10507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10516,10 +10521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45666</v>
+        <v>45611</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10532,7 +10537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10575,7 +10580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10589,10 +10594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45407</v>
+        <v>45784</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10605,7 +10610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10648,7 +10653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10658,14 +10663,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44948</v>
+        <v>45713</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10678,7 +10683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10721,7 +10726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10735,10 +10740,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45446</v>
+        <v>45576</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10751,7 +10756,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10794,7 +10799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10808,10 +10813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44943</v>
+        <v>45575</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10824,7 +10829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10867,7 +10872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10877,14 +10882,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45090</v>
+        <v>45713</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10896,13 +10901,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45611</v>
+        <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45784</v>
+        <v>45755</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45576</v>
+        <v>45827</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45575</v>
+        <v>45845</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11324,10 +11324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45645</v>
+        <v>45671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11393,14 +11393,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45713</v>
+        <v>45848</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11473,7 +11473,7 @@
         <v>44533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>46003</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45259</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44887</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45827</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45407</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>46049</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44706</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>45189</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45183</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44538</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>46169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45189</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>45834</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45855</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44886</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45265</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>44948</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45446</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45576</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>45104</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>45189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45236</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44572</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45471</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45433</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45433</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45825</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45799</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45433</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45259</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44914</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45260</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45671</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45666</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>46148</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45940</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>45713</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>45713</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>45385</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44977</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>45140</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44713</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45372</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44623</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45407</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>45407</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45203</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>46001</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>45433</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>44783</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>45191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>46029</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45152</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45282</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>46043</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>46049</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44664</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>46049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45446</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46059</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>46048</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45114</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>46008</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>46008</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>46184</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45090</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>46101</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>46101</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45014</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45217</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45210</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>46211</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>45433</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>45007</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>45611</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>45784</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>45713</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45576</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45575</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45713</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45755</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45825</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45827</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45845</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45848</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44533</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>46003</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46059</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE135"/>
+  <dimension ref="A1:AE138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45259</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>44887</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45827</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 16340-2024</t>
+          <t>A 5166-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45407</v>
+        <v>46049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2302,17 +2302,22 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2327,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2339,155 +2344,150 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 16340-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45407</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 16340-2024 artfynd.xlsx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 16340-2024 karta.png", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 16340-2024 georefererad karta.tif", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 16340-2024 FSC-klagomål.docx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 16340-2024 FSC-klagomål mail.docx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 16340-2024 tillsynsbegäran.docx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 16340-2024 tillsynsbegäran mail.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5166-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
         <v/>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44706</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>45189</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45183</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44538</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>46169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45189</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>45834</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>45530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45855</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44886</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45265</v>
+        <v>44948</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5050,14 +5050,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44948</v>
+        <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5130,7 +5130,7 @@
         <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45446</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45576</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45029</v>
+        <v>45104</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45104</v>
+        <v>45029</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5646,7 +5646,7 @@
         <v>45189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45236</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44572</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45471</v>
+        <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45433</v>
+        <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6077,7 +6077,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45433</v>
+        <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45825</v>
+        <v>45433</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45799</v>
+        <v>45433</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6306,14 +6306,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45104</v>
+        <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45433</v>
+        <v>45104</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45259</v>
+        <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44914</v>
+        <v>45671</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6544,13 +6544,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6593,7 +6588,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6607,10 +6602,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45671</v>
+        <v>45433</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6623,7 +6618,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6666,7 +6661,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6676,14 +6671,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45260</v>
+        <v>46148</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6696,7 +6691,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6739,7 +6734,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6753,10 +6748,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45671</v>
+        <v>45259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6769,7 +6764,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6812,7 +6807,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6826,10 +6821,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45671</v>
+        <v>45940</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6842,7 +6837,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6885,7 +6880,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6899,10 +6894,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45666</v>
+        <v>44914</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6914,8 +6909,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6958,7 +6958,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45701</v>
+        <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46148</v>
+        <v>45260</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7104,7 +7104,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45940</v>
+        <v>45666</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7177,7 +7177,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45713</v>
+        <v>45701</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7250,7 +7250,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7267,7 +7267,7 @@
         <v>45713</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45385</v>
+        <v>45713</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7352,13 +7352,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7401,7 +7396,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7411,14 +7406,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44977</v>
+        <v>45385</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7430,8 +7425,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45895</v>
+        <v>44977</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.2</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
         <v>45140</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44713</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44600</v>
+        <v>46001</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45372</v>
+        <v>44600</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7839,7 +7839,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7853,10 +7853,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44623</v>
+        <v>45372</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7912,7 +7912,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7926,10 +7926,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45407</v>
+        <v>45905</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7999,10 +7999,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45407</v>
+        <v>44623</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45203</v>
+        <v>46029</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8087,8 +8087,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8131,7 +8136,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8145,10 +8150,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46001</v>
+        <v>46029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8160,8 +8165,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8204,7 +8214,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8218,10 +8228,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45433</v>
+        <v>46184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8234,7 +8244,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8277,7 +8287,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8291,10 +8301,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44783</v>
+        <v>46043</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8307,7 +8317,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8350,7 +8360,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8364,10 +8374,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45191</v>
+        <v>46049</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8379,8 +8389,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>9.300000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8423,7 +8438,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8437,10 +8452,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46029</v>
+        <v>45407</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8452,13 +8467,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8501,7 +8511,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8515,10 +8525,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46029</v>
+        <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8530,13 +8540,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8579,7 +8584,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8589,14 +8594,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45163</v>
+        <v>45407</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8609,7 +8614,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8652,7 +8657,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8666,10 +8671,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45152</v>
+        <v>45203</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8682,7 +8687,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8725,7 +8730,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8735,14 +8740,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45282</v>
+        <v>46059</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8754,8 +8759,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8798,7 +8808,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8812,10 +8822,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46043</v>
+        <v>46048</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8828,7 +8838,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8871,7 +8881,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8885,10 +8895,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46049</v>
+        <v>45433</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8900,13 +8910,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8949,7 +8954,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8963,10 +8968,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44664</v>
+        <v>44783</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8979,7 +8984,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9022,7 +9027,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9036,10 +9041,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46049</v>
+        <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9051,8 +9056,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9095,7 +9105,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9109,10 +9119,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45446</v>
+        <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9124,8 +9134,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9168,7 +9183,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9182,10 +9197,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45905</v>
+        <v>45191</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9198,7 +9213,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9241,7 +9256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9251,14 +9266,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9271,7 +9286,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9314,7 +9329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9324,14 +9339,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46059</v>
+        <v>45152</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,13 +9358,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9392,7 +9402,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9406,10 +9416,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46048</v>
+        <v>46101</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9422,7 +9432,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9465,7 +9475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9479,10 +9489,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45114</v>
+        <v>46101</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9495,7 +9505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9538,7 +9548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9552,10 +9562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46008</v>
+        <v>45282</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9567,13 +9577,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9616,7 +9621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9630,10 +9635,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46008</v>
+        <v>44664</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9645,13 +9650,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46184</v>
+        <v>45446</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9777,14 +9777,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45090</v>
+        <v>45163</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9796,13 +9796,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9845,7 +9840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9859,10 +9854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46101</v>
+        <v>45114</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9875,7 +9870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9918,7 +9913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9928,14 +9923,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46101</v>
+        <v>45090</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9947,8 +9942,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9991,7 +9991,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45014</v>
+        <v>46211</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10020,8 +10020,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10064,7 +10069,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10078,10 +10083,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45666</v>
+        <v>45014</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10094,7 +10099,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10137,7 +10142,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10147,14 +10152,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45217</v>
+        <v>45666</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10167,7 +10172,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10210,7 +10215,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10220,14 +10225,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45210</v>
+        <v>45217</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10240,7 +10245,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10283,7 +10288,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10297,10 +10302,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46211</v>
+        <v>45210</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10312,13 +10317,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>4.5</v>
+        <v>0.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10378,7 +10378,7 @@
         <v>45433</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>45007</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10521,10 +10521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45611</v>
+        <v>46287</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10536,8 +10536,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10580,7 +10585,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10594,10 +10599,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45784</v>
+        <v>46286</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10609,8 +10614,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10653,7 +10663,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10663,14 +10673,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45713</v>
+        <v>46285</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10683,7 +10693,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10726,7 +10736,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10740,10 +10750,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45576</v>
+        <v>45611</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10756,7 +10766,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10799,7 +10809,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10813,10 +10823,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45575</v>
+        <v>45784</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10829,7 +10839,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10872,7 +10882,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10889,7 +10899,7 @@
         <v>45713</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10945,7 +10955,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10959,10 +10969,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45645</v>
+        <v>45576</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10975,7 +10985,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11028,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11032,10 +11042,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45755</v>
+        <v>45575</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11058,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11101,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11115,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45825</v>
+        <v>45713</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11131,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11174,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11188,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45827</v>
+        <v>45645</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11204,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11247,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11251,10 +11261,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45845</v>
+        <v>45755</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11267,7 +11277,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11310,7 +11320,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11324,10 +11334,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45671</v>
+        <v>45825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11340,7 +11350,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11393,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11393,14 +11403,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45848</v>
+        <v>45827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11413,7 +11423,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11456,24 +11466,24 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S 9900-2021</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44533</v>
+        <v>45845</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11486,7 +11496,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>28.1</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11529,153 +11539,372 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
+          <t>A 1879-2025</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>45671</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135" ht="15" customHeight="1">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>A 34780-2025</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>45848</v>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136" ht="15" customHeight="1">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>S 9900-2021</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>44533</v>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137" ht="15" customHeight="1">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>S 3504-2025</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D134" s="1" t="n">
+      <c r="D137" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="E134" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I134" t="n">
+      <c r="E137" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
         <v>0.2</v>
       </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>S 307-2026</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D135" s="1" t="n">
+      <c r="D138" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="E135" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
+      <c r="E138" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I135" t="n">
+      <c r="I138" t="n">
         <v>0.9</v>
       </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" s="2" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 22337-2024</t>
+          <t>A 56294-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45446</v>
+        <v>44887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1468,12 +1468,228 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata
+Skugglosta
+Myskmadra
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 30451-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Bokstumpbagge
+Gråbandad trägnagare
+Skogsveronika
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 22337-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Kransrams
@@ -1481,107 +1697,107 @@
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 60543-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45259</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trollfibbla
 Kransrams
@@ -1589,248 +1805,32 @@
 Tvåblad</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 56294-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44887</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Crunoecia irrorata
-Skugglosta
-Myskmadra
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30451-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45827</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Bokstumpbagge
-Gråbandad trägnagare
-Skogsveronika
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45471</v>
+        <v>45204</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2870,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2882,50 +2882,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2939,10 +2935,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45351</v>
+        <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2954,11 +2950,16 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2995,42 +2996,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3044,10 +3045,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44706</v>
+        <v>44538</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3061,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3069,13 +3070,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3087,48 +3088,48 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
@@ -3152,7 +3153,7 @@
         <v>45189</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3245,7 +3246,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3259,10 +3260,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45204</v>
+        <v>45834</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3275,7 +3276,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3311,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
@@ -3319,38 +3320,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3364,10 +3365,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46043</v>
+        <v>45253</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,19 +3381,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3404,58 +3405,58 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3469,10 +3470,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45183</v>
+        <v>45471</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3484,16 +3485,11 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3502,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3514,10 +3510,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3526,46 +3522,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44538</v>
+        <v>46169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3607,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3628,49 +3628,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45253</v>
+        <v>45530</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3700,82 +3700,82 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>16.6</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46169</v>
+        <v>45855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3845,42 +3845,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45189</v>
+        <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,25 +3909,20 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3942,55 +3937,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4004,10 +3999,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45834</v>
+        <v>45351</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4020,10 +4015,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4056,46 +4051,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4105,14 +4100,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45530</v>
+        <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4124,8 +4119,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>16.6</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4137,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4158,49 +4158,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45855</v>
+        <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4266,39 +4266,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44886</v>
+        <v>44783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44948</v>
+        <v>45713</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45265</v>
+        <v>45713</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44943</v>
+        <v>44477</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45446</v>
+        <v>45576</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44477</v>
+        <v>45433</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45187</v>
+        <v>45433</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5361,13 +5361,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5410,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5424,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45576</v>
+        <v>45701</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5440,7 +5435,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5483,7 +5478,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5497,10 +5492,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45104</v>
+        <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5513,7 +5508,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5556,7 +5551,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5570,10 +5565,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45029</v>
+        <v>45265</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5586,7 +5581,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5629,7 +5624,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5643,10 +5638,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45189</v>
+        <v>45825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5658,13 +5653,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5707,7 +5697,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5721,10 +5711,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45236</v>
+        <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5736,13 +5726,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5785,7 +5770,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5799,10 +5784,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44575</v>
+        <v>44572</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5815,7 +5800,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5858,7 +5843,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5872,10 +5857,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44572</v>
+        <v>45645</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5888,7 +5873,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5931,7 +5916,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5945,10 +5930,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45825</v>
+        <v>45713</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5961,7 +5946,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6004,7 +5989,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6018,10 +6003,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45471</v>
+        <v>44886</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6034,7 +6019,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6077,7 +6062,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6087,14 +6072,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45799</v>
+        <v>45104</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6107,7 +6092,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6150,7 +6135,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6164,10 +6149,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45433</v>
+        <v>45671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6180,7 +6165,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6223,7 +6208,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6237,10 +6222,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45433</v>
+        <v>45671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6253,7 +6238,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6296,7 +6281,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6313,7 +6298,7 @@
         <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6326,7 +6311,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6369,7 +6354,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6379,14 +6364,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45104</v>
+        <v>45940</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6399,7 +6384,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6442,7 +6427,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6456,10 +6441,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>45114</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6472,7 +6457,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6515,7 +6500,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6529,10 +6514,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45671</v>
+        <v>45372</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6545,7 +6530,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6588,7 +6573,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6602,10 +6587,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45433</v>
+        <v>45152</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6618,7 +6603,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6661,7 +6646,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6671,14 +6656,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46148</v>
+        <v>44664</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6691,7 +6676,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6734,7 +6719,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6748,10 +6733,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45259</v>
+        <v>45895</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6764,7 +6749,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6807,7 +6792,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6821,10 +6806,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45940</v>
+        <v>45576</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6837,7 +6822,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6880,7 +6865,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6894,10 +6879,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44914</v>
+        <v>45407</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6909,13 +6894,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6958,7 +6938,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6968,14 +6948,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45895</v>
+        <v>45140</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6988,7 +6968,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7031,7 +7011,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7045,10 +7025,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45260</v>
+        <v>45433</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7061,7 +7041,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7104,7 +7084,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7118,10 +7098,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45666</v>
+        <v>44623</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7134,7 +7114,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7177,7 +7157,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7191,10 +7171,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45701</v>
+        <v>45433</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7207,7 +7187,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7250,7 +7230,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7264,10 +7244,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45713</v>
+        <v>45446</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7280,7 +7260,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7323,7 +7303,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7337,10 +7317,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7353,7 +7333,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7396,7 +7376,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7410,10 +7390,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45385</v>
+        <v>45187</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7427,11 +7407,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7474,7 +7454,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7484,14 +7464,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44977</v>
+        <v>45259</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7504,7 +7484,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7547,7 +7527,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7557,14 +7537,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45140</v>
+        <v>45827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7577,7 +7557,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7620,7 +7600,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7634,10 +7614,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44713</v>
+        <v>45191</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7650,7 +7630,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7693,7 +7673,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7707,10 +7687,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46001</v>
+        <v>45014</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7723,7 +7703,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7766,7 +7746,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7780,10 +7760,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44600</v>
+        <v>45755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7796,7 +7776,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7839,7 +7819,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7853,10 +7833,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45372</v>
+        <v>45713</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7869,7 +7849,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7912,7 +7892,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7922,14 +7902,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45905</v>
+        <v>45217</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7942,7 +7922,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7985,7 +7965,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7999,10 +7979,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44623</v>
+        <v>45236</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8014,8 +7994,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8075,7 +8060,7 @@
         <v>46029</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8153,7 +8138,7 @@
         <v>46029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8214,7 +8199,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8228,10 +8213,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46184</v>
+        <v>46001</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8244,7 +8229,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8304,7 +8289,7 @@
         <v>46043</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8360,7 +8345,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8374,10 +8359,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46049</v>
+        <v>45471</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8389,13 +8374,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8438,7 +8418,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8452,10 +8432,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45407</v>
+        <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8467,8 +8447,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8528,7 +8513,7 @@
         <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8584,7 +8569,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8594,14 +8579,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45407</v>
+        <v>46285</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8614,7 +8599,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8657,7 +8642,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8671,10 +8656,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45203</v>
+        <v>45163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8687,7 +8672,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8730,7 +8715,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8740,14 +8725,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46059</v>
+        <v>46286</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8765,7 +8750,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8808,7 +8793,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8818,14 +8803,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46048</v>
+        <v>46059</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8835,6 +8820,11 @@
       <c r="G97" t="inlineStr">
         <is>
           <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -8881,7 +8871,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8895,10 +8885,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45433</v>
+        <v>46048</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8911,7 +8901,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8954,7 +8944,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8968,10 +8958,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44783</v>
+        <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8983,8 +8973,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9027,7 +9022,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9041,10 +9036,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46008</v>
+        <v>45385</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9058,11 +9053,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9105,7 +9100,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9119,10 +9114,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46008</v>
+        <v>46287</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9140,7 +9135,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9183,7 +9178,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9197,10 +9192,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45191</v>
+        <v>46008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9212,8 +9207,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>9.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9256,7 +9256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45163</v>
+        <v>45845</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9329,7 +9329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9343,10 +9343,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45152</v>
+        <v>44914</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9358,8 +9358,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9402,7 +9407,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9416,10 +9421,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46101</v>
+        <v>45203</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9432,7 +9437,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9492,7 +9497,7 @@
         <v>46101</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9548,7 +9553,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9562,10 +9567,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45282</v>
+        <v>46101</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9578,7 +9583,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9621,7 +9626,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9635,10 +9640,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44664</v>
+        <v>45007</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9651,7 +9656,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9699,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9708,10 +9713,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45446</v>
+        <v>45671</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9724,7 +9729,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9772,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9777,14 +9782,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45163</v>
+        <v>45848</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9797,7 +9802,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9840,7 +9845,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9854,10 +9859,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45114</v>
+        <v>44575</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9870,7 +9875,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9913,7 +9918,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9923,14 +9928,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45090</v>
+        <v>45282</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9942,13 +9947,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9991,7 +9991,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46211</v>
+        <v>45029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10020,13 +10020,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10069,7 +10064,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10083,10 +10078,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45014</v>
+        <v>45104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10099,7 +10094,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10142,7 +10137,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10156,10 +10151,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45666</v>
+        <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10172,7 +10167,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10215,7 +10210,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10225,14 +10220,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45217</v>
+        <v>45210</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10245,7 +10240,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10288,7 +10283,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10302,10 +10297,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45210</v>
+        <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10318,7 +10313,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10361,7 +10356,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10371,14 +10366,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45433</v>
+        <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10391,7 +10386,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10434,7 +10429,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10448,10 +10443,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45007</v>
+        <v>45799</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10464,7 +10459,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10507,7 +10502,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10521,10 +10516,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46287</v>
+        <v>44713</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10536,13 +10531,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10585,7 +10575,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10599,10 +10589,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46286</v>
+        <v>45189</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10620,7 +10610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10663,7 +10653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10673,14 +10663,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46285</v>
+        <v>45433</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10693,7 +10683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10736,7 +10726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10746,14 +10736,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45611</v>
+        <v>44977</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10766,7 +10756,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10809,7 +10799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10823,10 +10813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45784</v>
+        <v>45666</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10839,7 +10829,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10882,7 +10872,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10896,10 +10886,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45713</v>
+        <v>45407</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10912,7 +10902,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10955,7 +10945,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10965,14 +10955,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45576</v>
+        <v>44948</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11028,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11042,10 +11032,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45575</v>
+        <v>45446</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11058,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11101,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11115,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45713</v>
+        <v>44943</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11131,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11174,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11184,14 +11174,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45645</v>
+        <v>45090</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11203,8 +11193,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11247,7 +11242,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11257,14 +11252,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45755</v>
+        <v>46148</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11277,7 +11272,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11320,7 +11315,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11334,10 +11329,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45825</v>
+        <v>45611</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11350,7 +11345,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11393,7 +11388,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11407,10 +11402,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45827</v>
+        <v>45784</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11423,7 +11418,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11466,7 +11461,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11480,10 +11475,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45845</v>
+        <v>45905</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11496,7 +11491,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11539,7 +11534,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11553,10 +11548,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45671</v>
+        <v>46184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11569,7 +11564,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11612,7 +11607,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11622,14 +11617,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45848</v>
+        <v>46211</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11641,8 +11636,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11702,7 +11702,7 @@
         <v>44533</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46003</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 56294-2022</t>
+          <t>A 22337-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44887</v>
+        <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -1468,12 +1468,228 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Kransrams
+Myskmadra
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Trollfibbla
+Kransrams
+Stor häxört
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 56294-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44887</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Crunoecia irrorata
 Skugglosta
@@ -1481,107 +1697,107 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 30451-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45827</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2.1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Bokstumpbagge
 Gråbandad trägnagare
@@ -1589,248 +1805,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 22337-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Kransrams
-Myskmadra
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Trollfibbla
-Kransrams
-Stor häxört
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45204</v>
+        <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2870,10 +2870,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2882,46 +2882,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2935,10 +2939,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45189</v>
+        <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,16 +2954,11 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2996,42 +2995,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3045,10 +3044,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44538</v>
+        <v>44706</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,7 +3060,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3070,13 +3069,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3088,48 +3087,48 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
@@ -3153,7 +3152,7 @@
         <v>45189</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3245,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3260,10 +3259,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45834</v>
+        <v>45204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3276,7 +3275,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3312,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
@@ -3320,38 +3319,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3365,10 +3364,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45253</v>
+        <v>46043</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3381,82 +3380,82 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3470,10 +3469,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45471</v>
+        <v>45183</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3485,21 +3484,26 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3510,10 +3514,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3522,50 +3526,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46169</v>
+        <v>44538</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3607,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3628,49 +3628,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45530</v>
+        <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3700,13 +3700,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>16.6</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3724,58 +3724,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45855</v>
+        <v>46169</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3845,42 +3845,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44706</v>
+        <v>45189</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,20 +3909,25 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3937,55 +3942,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3999,10 +4004,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45351</v>
+        <v>45834</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4015,10 +4020,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4051,46 +4056,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4100,14 +4105,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45183</v>
+        <v>45530</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4119,13 +4124,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>16.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4137,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4158,49 +4158,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46043</v>
+        <v>45855</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4266,39 +4266,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44783</v>
+        <v>44886</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45713</v>
+        <v>44948</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45713</v>
+        <v>45265</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44477</v>
+        <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45576</v>
+        <v>45446</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45433</v>
+        <v>44477</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45433</v>
+        <v>45187</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5361,8 +5361,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5405,7 +5410,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5424,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45701</v>
+        <v>45029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5435,7 +5440,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5483,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5497,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45575</v>
+        <v>45104</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5508,7 +5513,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5556,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5565,10 +5570,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45265</v>
+        <v>45576</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5581,7 +5586,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5624,7 +5629,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5638,10 +5643,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45825</v>
+        <v>45189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5653,8 +5658,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5697,7 +5707,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5711,10 +5721,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45260</v>
+        <v>45236</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5726,8 +5736,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5770,7 +5785,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5784,10 +5799,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44572</v>
+        <v>44575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5800,7 +5815,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5843,7 +5858,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5857,10 +5872,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45645</v>
+        <v>45825</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5873,7 +5888,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5916,7 +5931,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5930,10 +5945,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45713</v>
+        <v>44572</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5946,7 +5961,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5989,7 +6004,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6003,10 +6018,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44886</v>
+        <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6019,7 +6034,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6062,7 +6077,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6072,14 +6087,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45104</v>
+        <v>45433</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6092,7 +6107,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6135,7 +6150,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6149,10 +6164,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45671</v>
+        <v>45433</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6165,7 +6180,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6208,7 +6223,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6225,7 +6240,7 @@
         <v>45671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6238,7 +6253,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6281,7 +6296,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6291,14 +6306,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45671</v>
+        <v>45104</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6311,7 +6326,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6354,7 +6369,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6368,10 +6383,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45940</v>
+        <v>45433</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6427,7 +6442,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6441,10 +6456,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45114</v>
+        <v>45799</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6457,7 +6472,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6500,7 +6515,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6514,10 +6529,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45372</v>
+        <v>45671</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6530,7 +6545,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6573,7 +6588,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6587,10 +6602,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45152</v>
+        <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6603,7 +6618,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6646,7 +6661,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6660,10 +6675,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44664</v>
+        <v>45259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6676,7 +6691,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6719,7 +6734,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6733,10 +6748,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45895</v>
+        <v>44914</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6748,8 +6763,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6792,7 +6812,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6806,10 +6826,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45576</v>
+        <v>45940</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6822,7 +6842,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6865,7 +6885,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6879,10 +6899,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45407</v>
+        <v>45260</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6895,7 +6915,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6938,7 +6958,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6948,14 +6968,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45140</v>
+        <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6968,7 +6988,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7011,7 +7031,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7025,10 +7045,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45433</v>
+        <v>45666</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7041,7 +7061,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7084,7 +7104,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7098,10 +7118,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44623</v>
+        <v>45701</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7114,7 +7134,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7157,7 +7177,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7171,10 +7191,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45433</v>
+        <v>45713</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7187,7 +7207,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7230,7 +7250,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7244,10 +7264,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45446</v>
+        <v>45713</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7260,7 +7280,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7303,7 +7323,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7317,10 +7337,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45825</v>
+        <v>45385</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7332,8 +7352,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7376,7 +7401,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7386,14 +7411,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45187</v>
+        <v>44977</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7405,13 +7430,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7454,7 +7474,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7464,14 +7484,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45259</v>
+        <v>45140</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7527,7 +7547,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7541,10 +7561,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45827</v>
+        <v>44713</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7557,7 +7577,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7600,7 +7620,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7610,14 +7630,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45191</v>
+        <v>46148</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7630,7 +7650,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>9.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7673,7 +7693,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7687,10 +7707,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45014</v>
+        <v>44600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7703,7 +7723,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7746,7 +7766,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7760,10 +7780,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45755</v>
+        <v>46001</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7776,7 +7796,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7819,7 +7839,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7833,10 +7853,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45713</v>
+        <v>45372</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7849,7 +7869,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7892,7 +7912,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7902,14 +7922,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45217</v>
+        <v>44623</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7922,7 +7942,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7965,7 +7985,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7979,10 +7999,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45236</v>
+        <v>46029</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7996,11 +8016,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8043,7 +8063,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8060,7 +8080,7 @@
         <v>46029</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8078,7 +8098,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8121,7 +8141,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8135,10 +8155,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46029</v>
+        <v>45407</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8150,13 +8170,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8199,7 +8214,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8213,10 +8228,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46001</v>
+        <v>45407</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8229,7 +8244,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8272,7 +8287,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8286,10 +8301,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46043</v>
+        <v>45203</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8302,7 +8317,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8345,7 +8360,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8359,10 +8374,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45471</v>
+        <v>46043</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8375,7 +8390,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8435,7 +8450,7 @@
         <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8513,7 +8528,7 @@
         <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8569,7 +8584,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8579,14 +8594,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46285</v>
+        <v>45433</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8599,7 +8614,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8642,7 +8657,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8652,14 +8667,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45163</v>
+        <v>46059</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8671,8 +8686,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8715,7 +8735,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8729,10 +8749,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46286</v>
+        <v>44783</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8744,13 +8764,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8793,7 +8808,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8803,14 +8818,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46059</v>
+        <v>45191</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8822,13 +8837,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8888,7 +8898,7 @@
         <v>46048</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8944,7 +8954,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8954,14 +8964,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46008</v>
+        <v>45163</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8973,13 +8983,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9022,7 +9027,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9036,10 +9041,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45385</v>
+        <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9053,11 +9058,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9100,7 +9105,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9114,10 +9119,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46287</v>
+        <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9135,7 +9140,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9178,7 +9183,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9192,10 +9197,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46008</v>
+        <v>45152</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9207,13 +9212,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9256,7 +9256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9270,10 +9270,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45845</v>
+        <v>45282</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9329,7 +9329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9343,10 +9343,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44914</v>
+        <v>45905</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9358,13 +9358,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9407,7 +9402,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9421,10 +9416,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45203</v>
+        <v>46101</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9437,7 +9432,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9480,7 +9475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9494,10 +9489,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46101</v>
+        <v>44664</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9510,7 +9505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9553,7 +9548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9567,10 +9562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46101</v>
+        <v>46184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9583,7 +9578,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9626,7 +9621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9640,10 +9635,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45007</v>
+        <v>45446</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9656,7 +9651,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9699,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9713,10 +9708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45671</v>
+        <v>46101</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9729,7 +9724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9772,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9782,14 +9777,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45848</v>
+        <v>45163</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9802,7 +9797,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9845,7 +9840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9859,10 +9854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44575</v>
+        <v>45114</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9875,7 +9870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9918,7 +9913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9928,14 +9923,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45282</v>
+        <v>45090</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9947,8 +9942,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9991,7 +9991,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45029</v>
+        <v>45014</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45104</v>
+        <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10147,14 +10147,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44600</v>
+        <v>45217</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10210,7 +10210,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45210</v>
+        <v>46211</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10239,8 +10239,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10283,7 +10288,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10297,10 +10302,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45666</v>
+        <v>45210</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10313,7 +10318,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10356,7 +10361,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10366,14 +10371,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45163</v>
+        <v>45433</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10386,7 +10391,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>9.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10429,7 +10434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10443,10 +10448,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45799</v>
+        <v>45007</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10459,7 +10464,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10502,7 +10507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10516,10 +10521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44713</v>
+        <v>45611</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10532,7 +10537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10575,7 +10580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10589,10 +10594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45189</v>
+        <v>45784</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10604,13 +10609,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10653,7 +10653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45433</v>
+        <v>46287</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10682,8 +10682,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10726,7 +10731,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10736,14 +10741,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44977</v>
+        <v>46286</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10755,8 +10760,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10799,7 +10809,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10809,14 +10819,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45666</v>
+        <v>46285</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10872,7 +10882,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10886,10 +10896,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45407</v>
+        <v>45713</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10902,7 +10912,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10945,7 +10955,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10955,14 +10965,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44948</v>
+        <v>45576</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11018,7 +11028,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11032,10 +11042,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45446</v>
+        <v>45575</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11058,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11101,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11115,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44943</v>
+        <v>45713</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11131,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11174,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11174,14 +11184,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45090</v>
+        <v>45645</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11193,13 +11203,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11242,7 +11247,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11252,14 +11257,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46148</v>
+        <v>45755</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11272,7 +11277,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11315,7 +11320,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11329,10 +11334,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45611</v>
+        <v>45825</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11345,7 +11350,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11388,7 +11393,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11402,10 +11407,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45784</v>
+        <v>45827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11418,7 +11423,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11461,7 +11466,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45905</v>
+        <v>45845</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11491,7 +11496,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11534,7 +11539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11548,10 +11553,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46184</v>
+        <v>45671</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11564,7 +11569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11607,7 +11612,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11617,14 +11622,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46211</v>
+        <v>45848</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11636,13 +11641,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11702,7 +11702,7 @@
         <v>44533</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46003</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE138"/>
+  <dimension ref="A1:AE137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 22337-2024</t>
+          <t>A 30451-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45446</v>
+        <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,21 +1459,237 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bokstumpbagge
+Gråbandad trägnagare
+Skogsveronika
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 56294-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44887</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata
+Skugglosta
+Myskmadra
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 22337-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Kransrams
@@ -1481,107 +1697,107 @@
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 60543-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45259</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trollfibbla
 Kransrams
@@ -1589,248 +1805,32 @@
 Tvåblad</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 56294-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44887</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Crunoecia irrorata
-Skugglosta
-Myskmadra
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30451-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45827</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Bokstumpbagge
-Gråbandad trägnagare
-Skogsveronika
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26736-2023</t>
+          <t>A 5166-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45090</v>
+        <v>46049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,20 +2196,25 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2224,164 +2229,159 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26736-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45090</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Månviol</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 5166-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45471</v>
+        <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,8 +2845,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2858,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2870,10 +2875,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2882,50 +2887,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2939,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45351</v>
+        <v>45204</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,10 +2956,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2995,42 +2996,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3044,10 +3045,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44706</v>
+        <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,19 +3061,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3087,55 +3088,55 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3149,10 +3150,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45189</v>
+        <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,13 +3165,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>16.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3203,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3214,38 +3210,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,14 +3251,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45204</v>
+        <v>45855</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3311,46 +3307,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3364,10 +3360,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46043</v>
+        <v>44538</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3376,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3392,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3413,49 +3409,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3469,10 +3465,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45183</v>
+        <v>46043</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3484,13 +3480,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3530,42 +3521,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3575,14 +3566,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44538</v>
+        <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3594,8 +3585,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3628,42 +3624,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
@@ -3687,7 +3683,7 @@
         <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3775,7 +3771,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3789,10 +3785,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46169</v>
+        <v>45471</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3805,10 +3801,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3817,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3829,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3845,42 +3841,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45189</v>
+        <v>46169</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,16 +3909,11 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3951,46 +3946,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4004,10 +3999,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45834</v>
+        <v>44706</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4020,19 +4015,19 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4047,55 +4042,55 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4105,14 +4100,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45530</v>
+        <v>45351</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4125,7 +4120,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>16.6</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4137,10 +4132,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4158,49 +4153,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4210,14 +4205,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45855</v>
+        <v>45183</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4229,11 +4224,16 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4266,39 +4266,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21424-2022</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44706</v>
+        <v>45713</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44886</v>
+        <v>44783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44948</v>
+        <v>45433</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45265</v>
+        <v>45433</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44943</v>
+        <v>45265</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45446</v>
+        <v>45260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44477</v>
+        <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45187</v>
+        <v>46029</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5410,7 +5410,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45029</v>
+        <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5439,8 +5439,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5483,7 +5488,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5497,10 +5502,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45104</v>
+        <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5513,7 +5518,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5556,7 +5561,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5570,10 +5575,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45576</v>
+        <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5586,7 +5591,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5629,7 +5634,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45189</v>
+        <v>45825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5658,13 +5663,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45236</v>
+        <v>45645</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5736,13 +5736,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5785,7 +5780,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44575</v>
+        <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5815,7 +5810,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5858,7 +5853,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45825</v>
+        <v>46043</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5931,7 +5926,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44572</v>
+        <v>46049</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5960,8 +5955,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45471</v>
+        <v>46049</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6077,7 +6077,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45433</v>
+        <v>45671</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6160,14 +6160,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45433</v>
+        <v>46059</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6179,8 +6179,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6223,7 +6228,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6237,10 +6242,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45671</v>
+        <v>46048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6253,7 +6258,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6296,7 +6301,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6306,14 +6311,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45104</v>
+        <v>46008</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6325,8 +6330,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6369,7 +6379,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6383,10 +6393,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45433</v>
+        <v>46008</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6398,8 +6408,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6442,7 +6457,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6456,10 +6471,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45799</v>
+        <v>45372</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6472,7 +6487,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6515,7 +6530,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6529,10 +6544,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45671</v>
+        <v>45152</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6545,7 +6560,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6605,7 +6620,7 @@
         <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6661,7 +6676,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6675,10 +6690,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45259</v>
+        <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6691,7 +6706,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6734,7 +6749,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6748,10 +6763,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44914</v>
+        <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6763,13 +6778,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6812,7 +6822,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6826,10 +6836,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45940</v>
+        <v>45576</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6842,7 +6852,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6885,7 +6895,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6899,10 +6909,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45260</v>
+        <v>46101</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6915,7 +6925,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6958,7 +6968,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6972,10 +6982,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45895</v>
+        <v>46101</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6988,7 +6998,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7031,7 +7041,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7045,10 +7055,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45666</v>
+        <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7061,7 +7071,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7104,7 +7114,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7118,10 +7128,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45701</v>
+        <v>45433</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7134,7 +7144,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7177,7 +7187,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7191,10 +7201,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45713</v>
+        <v>45014</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7207,7 +7217,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7267,7 +7277,7 @@
         <v>45713</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7323,7 +7333,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7337,10 +7347,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45385</v>
+        <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7352,13 +7362,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7401,7 +7406,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7411,14 +7416,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44977</v>
+        <v>46001</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7431,7 +7436,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7474,7 +7479,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7484,14 +7489,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45140</v>
+        <v>44477</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7504,7 +7509,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7547,7 +7552,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7561,10 +7566,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44713</v>
+        <v>45825</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7577,7 +7582,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7620,7 +7625,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7630,14 +7635,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46148</v>
+        <v>45827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7650,7 +7655,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7693,7 +7698,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7707,10 +7712,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44600</v>
+        <v>45755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7723,7 +7728,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7766,7 +7771,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7776,14 +7781,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46001</v>
+        <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7796,7 +7801,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7839,7 +7844,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7853,10 +7858,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45372</v>
+        <v>45701</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7869,7 +7874,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7912,7 +7917,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7926,10 +7931,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44623</v>
+        <v>45845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7942,7 +7947,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7985,7 +7990,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7999,10 +8004,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46029</v>
+        <v>45671</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8014,13 +8019,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8063,7 +8063,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8073,14 +8073,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46029</v>
+        <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8092,13 +8092,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8141,7 +8136,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8151,14 +8146,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45407</v>
+        <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8171,7 +8166,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8214,7 +8209,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8228,10 +8223,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45407</v>
+        <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8244,7 +8239,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8287,7 +8282,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8301,10 +8296,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45203</v>
+        <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8317,7 +8312,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8360,7 +8355,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8374,10 +8369,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46043</v>
+        <v>45114</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8390,7 +8385,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8433,7 +8428,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8447,10 +8442,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46049</v>
+        <v>44664</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8462,13 +8457,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8511,7 +8501,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8525,10 +8515,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46049</v>
+        <v>45407</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8541,7 +8531,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8584,7 +8574,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8598,10 +8588,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45433</v>
+        <v>46211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8613,8 +8603,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8657,7 +8652,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8667,14 +8662,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46059</v>
+        <v>45140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8686,13 +8681,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8735,7 +8725,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8749,10 +8739,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44783</v>
+        <v>44623</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8765,7 +8755,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8808,7 +8798,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8822,10 +8812,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45191</v>
+        <v>45433</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8838,7 +8828,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8881,7 +8871,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8895,10 +8885,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46048</v>
+        <v>45446</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8911,7 +8901,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8954,7 +8944,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8964,14 +8954,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45163</v>
+        <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8983,8 +8973,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>9.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9027,7 +9022,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9041,10 +9036,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46008</v>
+        <v>45259</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9056,13 +9051,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9105,7 +9095,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9119,10 +9109,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46008</v>
+        <v>45191</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9134,13 +9124,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9183,7 +9168,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9193,14 +9178,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45152</v>
+        <v>45217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9213,7 +9198,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9256,7 +9241,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9270,10 +9255,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45282</v>
+        <v>45236</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9285,8 +9270,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9329,7 +9319,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9343,10 +9333,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45905</v>
+        <v>45471</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9359,7 +9349,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>9.800000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9402,7 +9392,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9416,10 +9406,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46101</v>
+        <v>45163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9432,7 +9422,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9475,7 +9465,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9485,14 +9475,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44664</v>
+        <v>46285</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9505,7 +9495,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9548,7 +9538,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9562,10 +9552,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46184</v>
+        <v>46286</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9577,8 +9567,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9621,7 +9616,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9635,10 +9630,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45446</v>
+        <v>45385</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9650,8 +9645,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46101</v>
+        <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9723,8 +9723,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9772,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9781,10 +9786,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45163</v>
+        <v>44914</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9796,8 +9801,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9840,7 +9850,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9854,10 +9864,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45114</v>
+        <v>45203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9870,7 +9880,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9913,7 +9923,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9923,14 +9933,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45090</v>
+        <v>45007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9942,13 +9952,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9991,7 +9996,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10005,10 +10010,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45014</v>
+        <v>44575</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10021,7 +10026,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10064,7 +10069,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10078,10 +10083,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45666</v>
+        <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10094,7 +10099,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10137,7 +10142,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10147,14 +10152,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45217</v>
+        <v>45029</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10167,7 +10172,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10210,7 +10215,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10224,10 +10229,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46211</v>
+        <v>45104</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10239,13 +10244,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10288,7 +10288,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10302,10 +10302,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45210</v>
+        <v>44600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10361,7 +10361,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10375,10 +10375,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45433</v>
+        <v>45210</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10434,7 +10434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10448,10 +10448,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45007</v>
+        <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10507,7 +10507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10517,14 +10517,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45611</v>
+        <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10580,7 +10580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45784</v>
+        <v>44713</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10653,7 +10653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10667,10 +10667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46287</v>
+        <v>45189</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10731,7 +10731,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10745,10 +10745,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46286</v>
+        <v>45433</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10760,13 +10760,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10809,7 +10804,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10823,10 +10818,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46285</v>
+        <v>44977</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10839,7 +10834,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10882,7 +10877,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10896,10 +10891,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45713</v>
+        <v>45666</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10912,7 +10907,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10955,7 +10950,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10969,10 +10964,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45576</v>
+        <v>45407</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10985,7 +10980,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11028,7 +11023,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11038,14 +11033,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45575</v>
+        <v>44948</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11058,7 +11053,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11101,7 +11096,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11115,10 +11110,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45713</v>
+        <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11131,7 +11126,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11174,7 +11169,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11188,10 +11183,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45645</v>
+        <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11204,7 +11199,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11247,7 +11242,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11257,14 +11252,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45755</v>
+        <v>45090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11276,8 +11271,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11320,7 +11320,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11334,10 +11334,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45825</v>
+        <v>45611</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11393,7 +11393,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45827</v>
+        <v>45784</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11466,7 +11466,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45845</v>
+        <v>45713</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11553,10 +11553,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45671</v>
+        <v>45576</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11612,24 +11612,24 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>S 9900-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45848</v>
+        <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.1</v>
+        <v>28.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11685,7 +11685,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S 9900-2021</t>
+          <t>S 3504-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44533</v>
+        <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>28.1</v>
+        <v>0.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11755,10 +11755,10 @@
       </c>
       <c r="V136" s="2" t="inlineStr"/>
     </row>
-    <row r="137" ht="15" customHeight="1">
+    <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S 3504-2025</t>
+          <t>S 307-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11772,10 +11772,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46003</v>
+        <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11787,8 +11787,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11827,84 +11832,6 @@
         <v>0</v>
       </c>
       <c r="V137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>S 307-2026</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D138" s="1" t="n">
-        <v>46059</v>
-      </c>
-      <c r="E138" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I138" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" t="n">
-        <v>0</v>
-      </c>
-      <c r="U138" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>44887</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>45446</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45259</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>46049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45090</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45204</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45855</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44538</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>46043</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45471</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46169</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44706</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45351</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45183</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45713</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45433</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45433</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45265</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46029</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45645</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>46043</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>46049</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>46049</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45671</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46059</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46008</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>46008</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45372</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45152</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45576</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>46101</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>46101</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45433</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45014</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45713</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>46001</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44477</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45825</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45701</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45671</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45114</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44664</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45407</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>46211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44623</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45433</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45446</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45259</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45191</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>45217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45236</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45471</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>46285</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>46286</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45385</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44914</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>45203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>45007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44575</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45029</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45104</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>45210</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>44713</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>45189</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45433</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44977</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45666</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45407</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44948</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45611</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45784</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45713</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45576</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>44887</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>45446</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45259</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>46049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45090</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45204</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45855</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44538</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>46043</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45471</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46169</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44706</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45351</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45183</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45713</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45433</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45433</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45265</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44572</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46029</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45575</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45645</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45713</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>46043</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>46049</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>46049</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45671</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46059</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46048</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46008</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>46008</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45372</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45152</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45576</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>46101</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>46101</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45433</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45014</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45713</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>46001</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44477</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45825</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45701</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45671</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>46184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45114</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44664</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45407</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>46211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44623</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45433</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45446</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45259</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45191</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>45217</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45236</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45471</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>46285</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>46286</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45385</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44914</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>45203</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>45007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44575</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45029</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45104</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>45210</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>44713</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>45189</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45433</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44977</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>45666</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45407</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44948</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45611</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45784</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45713</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45576</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30451-2025</t>
+          <t>A 22337-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45827</v>
+        <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,21 +1459,129 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Kransrams
+Myskmadra
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 30451-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bokstumpbagge
 Gråbandad trägnagare
@@ -1481,107 +1589,215 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Trollfibbla
+Kransrams
+Stor häxört
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 56294-2022</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>44887</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Crunoecia irrorata
 Skugglosta
@@ -1589,248 +1805,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 22337-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Kransrams
-Myskmadra
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Trollfibbla
-Kransrams
-Stor häxört
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5166-2026</t>
+          <t>A 26736-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46049</v>
+        <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,25 +2196,20 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2229,159 +2224,164 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Månviol</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5166-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Entita
 Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26736-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45090</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Månviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45204</v>
+        <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
@@ -3000,38 +3000,38 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3041,14 +3041,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45834</v>
+        <v>45530</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,22 +3061,22 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>16.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3094,49 +3094,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45530</v>
+        <v>45855</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>16.6</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3178,10 +3178,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3199,49 +3199,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45855</v>
+        <v>45471</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3295,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3311,42 +3311,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3360,10 +3364,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44538</v>
+        <v>45351</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3376,7 +3380,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3388,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3409,49 +3413,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3465,10 +3469,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46043</v>
+        <v>44706</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3481,7 +3485,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3490,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3508,48 +3512,48 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
@@ -3573,7 +3577,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3670,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3680,10 +3684,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45253</v>
+        <v>45204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3696,20 +3700,20 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
@@ -3720,58 +3724,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3785,10 +3789,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45471</v>
+        <v>46043</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3801,20 +3805,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -3825,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3837,50 +3841,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46169</v>
+        <v>45183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,8 +3909,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3946,46 +3951,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3999,10 +4004,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44706</v>
+        <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4015,7 +4020,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4024,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4042,55 +4047,55 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45351</v>
+        <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4120,19 +4125,19 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4144,58 +4149,58 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4209,10 +4214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45183</v>
+        <v>46169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4224,13 +4229,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4266,39 +4266,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45713</v>
+        <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44783</v>
+        <v>45265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45433</v>
+        <v>44948</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45433</v>
+        <v>45713</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45265</v>
+        <v>45576</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45260</v>
+        <v>45825</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44572</v>
+        <v>45575</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46029</v>
+        <v>44943</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5361,13 +5361,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5410,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5424,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46029</v>
+        <v>45713</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5439,13 +5434,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5488,7 +5478,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5502,10 +5492,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45575</v>
+        <v>45645</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5518,7 +5508,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5561,7 +5551,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5575,10 +5565,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44886</v>
+        <v>45446</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5591,7 +5581,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5634,7 +5624,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5648,10 +5638,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45825</v>
+        <v>44477</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5664,7 +5654,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5707,7 +5697,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5721,10 +5711,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45645</v>
+        <v>45671</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5737,7 +5727,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5780,7 +5770,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5794,10 +5784,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45713</v>
+        <v>45755</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5810,7 +5800,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5853,7 +5843,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5867,10 +5857,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46043</v>
+        <v>45825</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5883,7 +5873,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5926,7 +5916,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5940,10 +5930,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46049</v>
+        <v>45187</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5957,11 +5947,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6004,7 +5994,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6018,10 +6008,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46049</v>
+        <v>45827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6034,7 +6024,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6077,7 +6067,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6094,7 +6084,7 @@
         <v>45671</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6107,7 +6097,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6150,7 +6140,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6160,14 +6150,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46059</v>
+        <v>45671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6179,13 +6169,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6228,7 +6213,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6242,10 +6227,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46048</v>
+        <v>45845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6258,7 +6243,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6301,7 +6286,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6315,10 +6300,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46008</v>
+        <v>45940</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6330,13 +6315,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6379,7 +6359,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6393,10 +6373,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46008</v>
+        <v>45029</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6408,13 +6388,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6457,7 +6432,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6471,10 +6446,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45372</v>
+        <v>45576</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6487,7 +6462,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6530,7 +6505,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6544,10 +6519,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45152</v>
+        <v>45104</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6560,7 +6535,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6603,7 +6578,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6620,7 +6595,7 @@
         <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6633,7 +6608,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6676,7 +6651,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6686,14 +6661,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45671</v>
+        <v>45848</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6706,7 +6681,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6749,7 +6724,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6763,10 +6738,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45940</v>
+        <v>45189</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6778,8 +6753,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6822,7 +6802,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6836,10 +6816,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45576</v>
+        <v>46029</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6851,8 +6831,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6895,7 +6880,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6909,10 +6894,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46101</v>
+        <v>46029</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6924,8 +6909,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6968,7 +6958,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6982,10 +6972,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46101</v>
+        <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6998,7 +6988,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7041,7 +7031,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7055,10 +7045,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45895</v>
+        <v>45236</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7070,8 +7060,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7114,7 +7109,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7128,10 +7123,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45433</v>
+        <v>44575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7144,7 +7139,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7187,7 +7182,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7201,10 +7196,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45014</v>
+        <v>46043</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7217,7 +7212,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7260,7 +7255,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7274,10 +7269,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45713</v>
+        <v>46049</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7289,8 +7284,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7333,7 +7333,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45799</v>
+        <v>46049</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>5.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46001</v>
+        <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7479,7 +7479,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44477</v>
+        <v>45471</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7552,7 +7552,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45825</v>
+        <v>46001</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7625,7 +7625,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45827</v>
+        <v>45433</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45755</v>
+        <v>45433</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46148</v>
+        <v>46059</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7800,8 +7800,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7844,7 +7849,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7858,10 +7863,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45701</v>
+        <v>46048</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7874,7 +7879,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7917,7 +7922,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7931,10 +7936,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45845</v>
+        <v>46008</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7946,8 +7951,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7990,7 +8000,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8004,10 +8014,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45671</v>
+        <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8019,8 +8029,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8063,7 +8078,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8077,10 +8092,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45848</v>
+        <v>45104</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8093,7 +8108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8136,7 +8151,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8146,14 +8161,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45104</v>
+        <v>45433</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8166,7 +8181,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8209,7 +8224,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8223,10 +8238,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45905</v>
+        <v>45259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8239,7 +8254,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8282,7 +8297,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8296,10 +8311,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46184</v>
+        <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8311,8 +8326,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8355,7 +8375,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8369,10 +8389,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45114</v>
+        <v>46101</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8385,7 +8405,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8428,7 +8448,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8442,10 +8462,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44664</v>
+        <v>45260</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8458,7 +8478,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8501,7 +8521,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8515,10 +8535,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45407</v>
+        <v>46101</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8531,7 +8551,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8574,7 +8594,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8588,10 +8608,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46211</v>
+        <v>45666</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8603,13 +8623,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8652,7 +8667,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8662,14 +8677,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45140</v>
+        <v>45701</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8725,7 +8740,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8739,10 +8754,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44623</v>
+        <v>45713</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8755,7 +8770,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8798,7 +8813,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8812,10 +8827,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45433</v>
+        <v>45713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8871,7 +8886,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8885,10 +8900,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45446</v>
+        <v>45385</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8900,8 +8915,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8944,7 +8964,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8954,14 +8974,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45187</v>
+        <v>44977</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8973,13 +8993,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9022,7 +9037,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9032,14 +9047,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45259</v>
+        <v>45140</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9095,7 +9110,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9109,10 +9124,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45191</v>
+        <v>44713</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9125,7 +9140,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>9.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9168,7 +9183,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9178,14 +9193,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45217</v>
+        <v>44600</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9198,7 +9213,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9241,7 +9256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9255,10 +9270,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45236</v>
+        <v>45372</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9270,13 +9285,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9319,7 +9329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9333,10 +9343,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45471</v>
+        <v>44623</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9349,7 +9359,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9392,7 +9402,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9406,10 +9416,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45163</v>
+        <v>45799</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9422,7 +9432,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9465,7 +9475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9475,14 +9485,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46285</v>
+        <v>45407</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9495,7 +9505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9538,7 +9548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9552,10 +9562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46286</v>
+        <v>45407</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9567,13 +9577,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9616,7 +9621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9630,10 +9635,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45385</v>
+        <v>45203</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9645,13 +9650,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9704,14 +9704,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46287</v>
+        <v>46148</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9723,13 +9723,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9772,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9786,10 +9781,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44914</v>
+        <v>45433</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9801,13 +9796,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9850,7 +9840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9864,10 +9854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45203</v>
+        <v>44783</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9880,7 +9870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9923,7 +9913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9937,10 +9927,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45007</v>
+        <v>45191</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9953,7 +9943,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9996,7 +9986,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10006,14 +9996,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44575</v>
+        <v>45163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10026,7 +10016,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10069,7 +10059,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10083,10 +10073,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45282</v>
+        <v>45152</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10099,7 +10089,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10142,7 +10132,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10156,10 +10146,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45029</v>
+        <v>45282</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10172,7 +10162,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10215,7 +10205,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10229,10 +10219,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45104</v>
+        <v>44664</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10245,7 +10235,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10288,7 +10278,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10302,10 +10292,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44600</v>
+        <v>45446</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10361,7 +10351,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10375,10 +10365,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45210</v>
+        <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10391,7 +10381,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.1</v>
+        <v>3.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10434,7 +10424,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10448,10 +10438,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45666</v>
+        <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10464,7 +10454,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10507,7 +10497,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10517,14 +10507,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45163</v>
+        <v>45114</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10537,7 +10527,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>9.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10580,7 +10570,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10594,10 +10584,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44713</v>
+        <v>46184</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10610,7 +10600,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10653,7 +10643,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10663,14 +10653,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45189</v>
+        <v>45090</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10688,7 +10678,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10731,7 +10721,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10745,10 +10735,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45433</v>
+        <v>45014</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10761,7 +10751,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10804,7 +10794,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10814,14 +10804,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44977</v>
+        <v>45666</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10834,7 +10824,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10877,7 +10867,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10887,14 +10877,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45666</v>
+        <v>45217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10907,7 +10897,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10950,7 +10940,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10964,10 +10954,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45407</v>
+        <v>46211</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10979,8 +10969,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11023,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11033,14 +11028,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44948</v>
+        <v>45210</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11053,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11096,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11110,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45446</v>
+        <v>45433</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11126,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11169,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11183,10 +11178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44943</v>
+        <v>45007</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11199,7 +11194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11242,7 +11237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11252,14 +11247,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45090</v>
+        <v>45611</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11271,13 +11266,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11320,7 +11310,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11334,10 +11324,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45611</v>
+        <v>45784</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11350,7 +11340,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11393,7 +11383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11407,10 +11397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45784</v>
+        <v>46287</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11422,8 +11412,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11466,7 +11461,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11480,10 +11475,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45713</v>
+        <v>46286</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11495,8 +11490,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11549,14 +11549,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45576</v>
+        <v>46285</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 22337-2024</t>
+          <t>A 30451-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45446</v>
+        <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,21 +1459,237 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bokstumpbagge
+Gråbandad trägnagare
+Skogsveronika
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 56294-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44887</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata
+Skugglosta
+Myskmadra
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 22337-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Kransrams
@@ -1481,215 +1697,107 @@
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 30451-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>45827</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="D12" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Bokstumpbagge
-Gråbandad trägnagare
-Skogsveronika
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Trollfibbla
 Kransrams
@@ -1697,140 +1805,32 @@
 Tvåblad</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 56294-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44887</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Crunoecia irrorata
-Skugglosta
-Myskmadra
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26736-2023</t>
+          <t>A 5166-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45090</v>
+        <v>46049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,20 +2196,25 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2224,164 +2229,159 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26736-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45090</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Månviol</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 5166-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45530</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45855</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,10 +3255,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45471</v>
+        <v>45204</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3295,10 +3295,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3307,50 +3307,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3364,10 +3360,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45351</v>
+        <v>44538</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3376,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3392,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3413,49 +3409,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3465,14 +3461,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44706</v>
+        <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3484,8 +3480,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3494,13 +3495,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3512,55 +3513,55 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3570,14 +3571,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45189</v>
+        <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3589,19 +3590,14 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3610,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3619,58 +3615,58 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3684,10 +3680,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45204</v>
+        <v>45471</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3700,7 +3696,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3712,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3724,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3736,39 +3732,43 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
         <v>46043</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45183</v>
+        <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3909,13 +3909,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3924,10 +3919,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3942,55 +3937,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4004,10 +3999,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44538</v>
+        <v>45351</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4020,7 +4015,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4032,10 +4027,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4053,49 +4048,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4109,10 +4104,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45253</v>
+        <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4124,76 +4119,81 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
         <v>46169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44886</v>
+        <v>45713</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45265</v>
+        <v>44783</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44948</v>
+        <v>45433</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45713</v>
+        <v>45433</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45576</v>
+        <v>45265</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45825</v>
+        <v>45260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44943</v>
+        <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45713</v>
+        <v>45575</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45645</v>
+        <v>45825</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45446</v>
+        <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44477</v>
+        <v>46029</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5653,8 +5653,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5697,7 +5702,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5711,10 +5716,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45671</v>
+        <v>46029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5726,8 +5731,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5770,7 +5780,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45755</v>
+        <v>45645</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5800,7 +5810,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5843,7 +5853,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5857,10 +5867,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45825</v>
+        <v>45713</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5873,7 +5883,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5916,7 +5926,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5930,10 +5940,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45187</v>
+        <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5945,13 +5955,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5994,7 +5999,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6008,10 +6013,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45827</v>
+        <v>45671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6024,7 +6029,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6067,7 +6072,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6081,10 +6086,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45671</v>
+        <v>45827</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6097,7 +6102,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6140,7 +6145,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6154,10 +6159,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45671</v>
+        <v>45755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6170,7 +6175,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6213,7 +6218,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6227,10 +6232,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45845</v>
+        <v>46043</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6243,7 +6248,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6286,7 +6291,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6300,10 +6305,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45940</v>
+        <v>45372</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6316,7 +6321,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6359,7 +6364,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6373,10 +6378,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45029</v>
+        <v>45152</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6389,7 +6394,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6432,7 +6437,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45576</v>
+        <v>45671</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6505,7 +6510,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45104</v>
+        <v>45671</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6535,7 +6540,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6578,7 +6583,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6592,10 +6597,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45671</v>
+        <v>45845</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6608,7 +6613,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6651,7 +6656,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6661,14 +6666,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45848</v>
+        <v>45940</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6681,7 +6686,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6724,7 +6729,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6738,10 +6743,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45189</v>
+        <v>45671</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6753,13 +6758,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6802,7 +6802,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46029</v>
+        <v>45576</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6831,13 +6831,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6880,7 +6875,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6890,14 +6885,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46029</v>
+        <v>45848</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6909,13 +6904,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6958,7 +6948,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6972,10 +6962,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45895</v>
+        <v>46049</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6987,8 +6977,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7031,7 +7026,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7045,10 +7040,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45236</v>
+        <v>46049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7060,13 +7055,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7109,7 +7099,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7123,10 +7113,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44575</v>
+        <v>45895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7139,7 +7129,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7182,7 +7172,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7192,14 +7182,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46043</v>
+        <v>46059</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7211,8 +7201,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7255,7 +7250,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7269,10 +7264,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46049</v>
+        <v>45433</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7284,13 +7279,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7333,7 +7323,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7347,10 +7337,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46049</v>
+        <v>46048</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7363,7 +7353,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7406,7 +7396,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7420,10 +7410,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44572</v>
+        <v>46008</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7435,8 +7425,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7479,7 +7474,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7493,10 +7488,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45471</v>
+        <v>45014</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7509,7 +7504,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7552,7 +7547,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7566,10 +7561,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7581,8 +7576,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7625,7 +7625,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45433</v>
+        <v>45713</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45433</v>
+        <v>46001</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46059</v>
+        <v>46101</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7800,13 +7800,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7849,7 +7844,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7863,10 +7858,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46048</v>
+        <v>46101</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7879,7 +7874,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7922,7 +7917,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7936,10 +7931,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46008</v>
+        <v>44477</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7951,13 +7946,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8000,7 +7990,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8014,10 +8004,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46008</v>
+        <v>45701</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8029,13 +8019,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8078,7 +8063,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8088,14 +8073,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45104</v>
+        <v>45799</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8108,7 +8093,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8151,7 +8136,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8161,14 +8146,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45433</v>
+        <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8181,7 +8166,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8224,7 +8209,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8238,10 +8223,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45259</v>
+        <v>45114</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8254,7 +8239,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8297,7 +8282,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8307,14 +8292,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44914</v>
+        <v>46148</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8326,13 +8311,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8375,7 +8355,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8389,10 +8369,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46101</v>
+        <v>44664</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8405,7 +8385,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8448,7 +8428,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8462,10 +8442,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45260</v>
+        <v>45407</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8478,7 +8458,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8521,7 +8501,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8531,14 +8511,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46101</v>
+        <v>45140</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8551,7 +8531,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8594,7 +8574,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8608,10 +8588,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45666</v>
+        <v>44623</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8624,7 +8604,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8667,7 +8647,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8681,10 +8661,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45701</v>
+        <v>45433</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8697,7 +8677,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8740,7 +8720,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8754,10 +8734,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45713</v>
+        <v>45446</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8770,7 +8750,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8813,7 +8793,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8827,10 +8807,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45713</v>
+        <v>45187</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8842,8 +8822,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8886,7 +8871,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8900,10 +8885,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45385</v>
+        <v>45259</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8915,13 +8900,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8964,7 +8944,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8974,14 +8954,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44977</v>
+        <v>45191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8994,7 +8974,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9037,7 +9017,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9051,10 +9031,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45140</v>
+        <v>45217</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9067,7 +9047,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9110,7 +9090,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9124,10 +9104,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44713</v>
+        <v>45236</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9139,8 +9119,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9183,7 +9168,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9197,10 +9182,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44600</v>
+        <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9213,7 +9198,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9256,7 +9241,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9270,10 +9255,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45372</v>
+        <v>46184</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9286,7 +9271,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9329,7 +9314,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9343,10 +9328,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44623</v>
+        <v>45471</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9359,7 +9344,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9402,7 +9387,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9416,10 +9401,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45799</v>
+        <v>45163</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9432,7 +9417,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9475,7 +9460,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9489,10 +9474,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45407</v>
+        <v>45385</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9504,8 +9489,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9548,7 +9538,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9562,10 +9552,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45407</v>
+        <v>46211</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9577,8 +9567,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9621,7 +9616,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9635,10 +9630,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45203</v>
+        <v>44914</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9650,8 +9645,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9704,14 +9704,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46148</v>
+        <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45433</v>
+        <v>45007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44783</v>
+        <v>44575</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9913,7 +9913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45191</v>
+        <v>45282</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>9.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9986,7 +9986,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9996,14 +9996,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45163</v>
+        <v>45029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>9.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45152</v>
+        <v>45104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10132,7 +10132,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45282</v>
+        <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10205,7 +10205,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44664</v>
+        <v>45210</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45446</v>
+        <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10351,7 +10351,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10361,14 +10361,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10424,7 +10424,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45905</v>
+        <v>44713</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10497,7 +10497,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10511,10 +10511,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45114</v>
+        <v>45189</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10526,8 +10526,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10570,7 +10575,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10584,10 +10589,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46184</v>
+        <v>45433</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10600,7 +10605,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10643,7 +10648,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10657,10 +10662,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45090</v>
+        <v>44977</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10672,13 +10677,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10721,7 +10721,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10735,10 +10735,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45014</v>
+        <v>45666</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10808,10 +10808,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45666</v>
+        <v>45407</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45217</v>
+        <v>46285</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10940,7 +10940,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46211</v>
+        <v>46286</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10971,11 +10971,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11028,14 +11028,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45210</v>
+        <v>44948</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45433</v>
+        <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11164,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11178,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45007</v>
+        <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11237,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11247,14 +11247,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45611</v>
+        <v>45090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11266,8 +11266,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11310,7 +11315,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11324,10 +11329,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45784</v>
+        <v>46287</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11339,8 +11344,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11393,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11397,10 +11407,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46287</v>
+        <v>45611</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11412,13 +11422,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11461,7 +11466,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46286</v>
+        <v>45784</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11490,13 +11495,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11549,14 +11549,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46285</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30451-2025</t>
+          <t>A 56294-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45827</v>
+        <v>44887</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1471,9 +1471,225 @@
         <v>4</v>
       </c>
       <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Crunoecia irrorata
+Skugglosta
+Myskmadra
+Strävlosta</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 22337-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45446</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Kransrams
+Myskmadra
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 30451-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Bokstumpbagge
 Gråbandad trägnagare
@@ -1481,248 +1697,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 56294-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44887</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Crunoecia irrorata
-Skugglosta
-Myskmadra
-Strävlosta</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 22337-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Kransrams
-Myskmadra
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>45259</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5166-2026</t>
+          <t>A 16340-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46049</v>
+        <v>45407</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,22 +2196,17 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2226,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2238,256 +2233,261 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Lövgroda
+Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 16340-2024 artfynd.xlsx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 16340-2024 karta.png", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 16340-2024 georefererad karta.tif", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 16340-2024 FSC-klagomål.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 16340-2024 FSC-klagomål mail.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 16340-2024 tillsynsbegäran.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 16340-2024 tillsynsbegäran mail.docx", "A 16340-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26736-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45090</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Månviol</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5166-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Entita
 Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26736-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45090</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Månviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 16340-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45407</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lövgroda
-Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 16340-2024 artfynd.xlsx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 16340-2024 karta.png", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 16340-2024 georefererad karta.tif", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 16340-2024 FSC-klagomål.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 16340-2024 FSC-klagomål mail.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 16340-2024 tillsynsbegäran.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 16340-2024 tillsynsbegäran mail.docx", "A 16340-2024")</f>
         <v/>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2847,26 +2847,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2887,46 +2887,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45834</v>
+        <v>45204</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
@@ -3000,38 +3000,38 @@
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3041,14 +3041,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45530</v>
+        <v>45471</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>16.6</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3085,58 +3085,62 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3146,14 +3150,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45855</v>
+        <v>45351</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,10 +3170,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3202,46 +3206,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,10 +3259,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45204</v>
+        <v>45189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3270,8 +3274,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3315,38 +3324,38 @@
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3360,10 +3369,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44538</v>
+        <v>45183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3375,8 +3384,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3388,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3409,49 +3423,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3461,14 +3475,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>45834</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3480,16 +3494,11 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3498,10 +3507,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3526,42 +3535,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3575,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45253</v>
+        <v>44538</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3591,82 +3600,82 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3676,14 +3685,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45471</v>
+        <v>45530</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3696,23 +3705,23 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>16.6</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
@@ -3720,62 +3729,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3789,10 +3794,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46043</v>
+        <v>45253</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3805,19 +3810,19 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3829,58 +3834,58 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3890,14 +3895,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44706</v>
+        <v>45855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3910,19 +3915,19 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3937,55 +3942,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3999,10 +4004,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45351</v>
+        <v>44706</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4015,7 +4020,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4024,10 +4029,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4042,55 +4047,55 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45183</v>
+        <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4119,13 +4124,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4165,35 +4165,35 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
         <v>46169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45713</v>
+        <v>44575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44783</v>
+        <v>45407</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45433</v>
+        <v>45407</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45433</v>
+        <v>45203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45265</v>
+        <v>45433</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45260</v>
+        <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45576</v>
+        <v>45191</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44572</v>
+        <v>45433</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45575</v>
+        <v>44572</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45825</v>
+        <v>45471</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44886</v>
+        <v>45163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46029</v>
+        <v>45152</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5653,13 +5653,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5702,7 +5697,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5716,10 +5711,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46029</v>
+        <v>45433</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5731,13 +5726,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5780,7 +5770,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5794,10 +5784,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45645</v>
+        <v>45433</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5810,7 +5800,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5853,7 +5843,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5867,10 +5857,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45713</v>
+        <v>45282</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5883,7 +5873,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5926,7 +5916,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5940,10 +5930,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45825</v>
+        <v>45007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5956,7 +5946,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5999,7 +5989,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6013,10 +6003,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45671</v>
+        <v>44664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6029,7 +6019,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6072,7 +6062,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6086,10 +6076,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45827</v>
+        <v>44886</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6102,7 +6092,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6145,7 +6135,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6159,10 +6149,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45755</v>
+        <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6175,7 +6165,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6218,7 +6208,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6232,10 +6222,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46043</v>
+        <v>45265</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6248,7 +6238,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6291,7 +6281,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6305,10 +6295,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45372</v>
+        <v>45163</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6321,7 +6311,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6364,7 +6354,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6374,14 +6364,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45152</v>
+        <v>44948</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6394,7 +6384,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6437,7 +6427,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6447,14 +6437,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45671</v>
+        <v>45104</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6467,7 +6457,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6510,7 +6500,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6524,10 +6514,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45671</v>
+        <v>45433</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6540,7 +6530,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6583,7 +6573,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6597,10 +6587,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45845</v>
+        <v>45259</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6613,7 +6603,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6656,7 +6646,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6670,10 +6660,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45940</v>
+        <v>45114</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6686,7 +6676,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6729,7 +6719,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6743,10 +6733,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45671</v>
+        <v>45611</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6759,7 +6749,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6802,7 +6792,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6816,10 +6806,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45576</v>
+        <v>44914</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6831,8 +6821,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6875,7 +6870,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6885,14 +6880,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45848</v>
+        <v>45784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6905,7 +6900,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6948,7 +6943,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6962,10 +6957,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46049</v>
+        <v>45260</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6977,13 +6972,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7026,7 +7016,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7036,14 +7026,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46049</v>
+        <v>45090</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7055,8 +7045,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7099,7 +7094,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7113,10 +7108,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45895</v>
+        <v>45713</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7129,7 +7124,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7172,7 +7167,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7182,14 +7177,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46059</v>
+        <v>45576</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7201,13 +7196,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7250,7 +7240,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7264,10 +7254,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45433</v>
+        <v>45666</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7280,7 +7270,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7323,7 +7313,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7337,10 +7327,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46048</v>
+        <v>44943</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7353,7 +7343,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7396,7 +7386,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7410,10 +7400,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46008</v>
+        <v>45446</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7425,13 +7415,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7474,7 +7459,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7488,10 +7473,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45014</v>
+        <v>45701</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7504,7 +7489,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7547,7 +7532,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7561,10 +7546,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46008</v>
+        <v>45575</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7576,13 +7561,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7625,7 +7605,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7639,10 +7619,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45713</v>
+        <v>44477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7655,7 +7635,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7698,7 +7678,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7712,10 +7692,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46001</v>
+        <v>45713</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7728,7 +7708,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7771,7 +7751,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7785,10 +7765,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46101</v>
+        <v>45645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7801,7 +7781,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7844,7 +7824,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7858,10 +7838,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46101</v>
+        <v>45014</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7874,7 +7854,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7917,7 +7897,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7931,10 +7911,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44477</v>
+        <v>45713</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7947,7 +7927,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7990,7 +7970,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8004,10 +7984,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45701</v>
+        <v>45713</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8020,7 +8000,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8063,7 +8043,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8077,10 +8057,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45799</v>
+        <v>45385</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8092,8 +8072,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8136,7 +8121,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8150,10 +8135,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45104</v>
+        <v>44977</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8166,7 +8151,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8209,7 +8194,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8223,10 +8208,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45114</v>
+        <v>45666</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8239,7 +8224,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8282,7 +8267,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8296,10 +8281,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46148</v>
+        <v>45140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8312,7 +8297,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8355,7 +8340,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8369,10 +8354,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44664</v>
+        <v>44713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8385,7 +8370,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8428,7 +8413,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8442,10 +8427,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45407</v>
+        <v>45187</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8457,8 +8442,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8501,7 +8491,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8511,14 +8501,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45140</v>
+        <v>44600</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8531,7 +8521,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8574,7 +8564,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8584,14 +8574,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44623</v>
+        <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8604,7 +8594,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8647,7 +8637,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8661,10 +8651,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45433</v>
+        <v>45755</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8677,7 +8667,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8720,7 +8710,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8734,10 +8724,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45446</v>
+        <v>45825</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8750,7 +8740,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8793,7 +8783,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8807,10 +8797,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45187</v>
+        <v>45827</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8822,13 +8812,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8871,7 +8856,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8885,10 +8870,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45259</v>
+        <v>45372</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8901,7 +8886,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8944,7 +8929,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8958,10 +8943,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45191</v>
+        <v>44623</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8974,7 +8959,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>9.300000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9017,7 +9002,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9027,14 +9012,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45217</v>
+        <v>45210</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9047,7 +9032,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9090,7 +9075,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9104,10 +9089,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45236</v>
+        <v>45845</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9119,13 +9104,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9168,7 +9148,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9182,10 +9162,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45905</v>
+        <v>45029</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9198,7 +9178,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9241,7 +9221,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9255,10 +9235,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46184</v>
+        <v>45671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9271,7 +9251,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9314,7 +9294,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9324,14 +9304,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45471</v>
+        <v>45848</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9344,7 +9324,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9387,7 +9367,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9401,10 +9381,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45163</v>
+        <v>45576</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9417,7 +9397,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9460,7 +9440,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9474,10 +9454,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45385</v>
+        <v>45104</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9489,13 +9469,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9538,7 +9513,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9552,10 +9527,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46211</v>
+        <v>45189</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9569,11 +9544,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9616,7 +9591,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9630,10 +9605,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44914</v>
+        <v>45236</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9647,11 +9622,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9669,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9708,10 +9683,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45203</v>
+        <v>45940</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9724,7 +9699,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9742,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9781,10 +9756,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45007</v>
+        <v>45825</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9797,7 +9772,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9840,7 +9815,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9854,10 +9829,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44575</v>
+        <v>45895</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9870,7 +9845,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9913,7 +9888,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9927,10 +9902,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45282</v>
+        <v>45671</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9943,7 +9918,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9986,7 +9961,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10000,10 +9975,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45029</v>
+        <v>45671</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10016,7 +9991,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10059,7 +10034,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10073,10 +10048,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45104</v>
+        <v>45671</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10089,7 +10064,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10132,7 +10107,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10146,10 +10121,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44600</v>
+        <v>46001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10162,7 +10137,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10205,7 +10180,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10219,10 +10194,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45210</v>
+        <v>46029</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10234,8 +10209,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.1</v>
+        <v>6.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10278,7 +10258,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10292,10 +10272,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45666</v>
+        <v>46029</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10307,8 +10287,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10351,7 +10336,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10361,14 +10346,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45163</v>
+        <v>46043</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10381,7 +10366,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>9.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10424,7 +10409,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10438,10 +10423,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44713</v>
+        <v>46049</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10453,8 +10438,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10497,7 +10487,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10511,10 +10501,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45189</v>
+        <v>46049</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10526,13 +10516,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10575,7 +10560,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10585,14 +10570,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45433</v>
+        <v>46059</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10604,8 +10589,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10648,7 +10638,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10658,14 +10648,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44977</v>
+        <v>46048</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10678,7 +10668,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10721,7 +10711,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10735,10 +10725,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45666</v>
+        <v>46008</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10750,8 +10740,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10794,7 +10789,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10808,10 +10803,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45407</v>
+        <v>46008</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10823,8 +10818,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10877,14 +10877,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46285</v>
+        <v>46101</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10940,7 +10940,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46286</v>
+        <v>46101</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10969,13 +10969,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11018,7 +11013,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11028,14 +11023,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44948</v>
+        <v>45799</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11048,7 +11043,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11091,7 +11086,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11101,14 +11096,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45446</v>
+        <v>46148</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11121,7 +11116,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11164,7 +11159,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11178,10 +11173,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44943</v>
+        <v>45905</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11194,7 +11189,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11237,7 +11232,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11247,14 +11242,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45090</v>
+        <v>46184</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11266,13 +11261,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11315,7 +11305,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11329,10 +11319,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46287</v>
+        <v>46211</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11346,11 +11336,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11393,7 +11383,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11407,10 +11397,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45611</v>
+        <v>46287</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11422,8 +11412,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11466,7 +11461,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11480,10 +11475,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45784</v>
+        <v>46286</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11495,8 +11490,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11549,14 +11549,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45713</v>
+        <v>46285</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 56294-2022</t>
+          <t>A 30451-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44887</v>
+        <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1471,9 +1471,117 @@
         <v>4</v>
       </c>
       <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Bokstumpbagge
+Gråbandad trägnagare
+Skogsveronika
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 56294-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44887</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Crunoecia irrorata
 Skugglosta
@@ -1481,107 +1589,107 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 22337-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45446</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>12.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Fläcklungört
 Kransrams
@@ -1589,140 +1697,32 @@
 Skogsknipprot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 30451-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45827</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Bokstumpbagge
-Gråbandad trägnagare
-Skogsveronika
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>45259</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 16340-2024</t>
+          <t>A 5166-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45407</v>
+        <v>46049</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,17 +2196,22 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2221,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2233,261 +2238,256 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26736-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45090</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Månviol</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 16340-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45407</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Lövgroda
 Större vattensalamander</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 16340-2024 artfynd.xlsx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 16340-2024 karta.png", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 16340-2024 georefererad karta.tif", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 16340-2024 FSC-klagomål.docx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 16340-2024 FSC-klagomål mail.docx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 16340-2024 tillsynsbegäran.docx", "A 16340-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 16340-2024 tillsynsbegäran mail.docx", "A 16340-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26736-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45090</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Månviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5166-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
         <v/>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45925-2023</t>
+          <t>A 44580-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2847,14 +2847,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2863,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2887,39 +2887,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
         <v/>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
         <v>45204</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45471</v>
+        <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3085,10 +3085,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3101,46 +3101,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3150,14 +3146,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45351</v>
+        <v>45530</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3170,7 +3166,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>16.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3182,10 +3178,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3203,49 +3199,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44580-2023</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,14 +3251,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45189</v>
+        <v>45855</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3274,13 +3270,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3316,46 +3307,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 44580-2023 artfynd.xlsx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 44580-2023 karta.png", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 44580-2023 georefererad karta.tif", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 44580-2023 FSC-klagomål.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 44580-2023 FSC-klagomål mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 44580-2023 tillsynsbegäran.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 44580-2023 tillsynsbegäran mail.docx", "A 44580-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,10 +3360,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45183</v>
+        <v>44538</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3384,13 +3375,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3402,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3423,49 +3409,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3465,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45834</v>
+        <v>46043</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,10 +3481,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3531,46 +3517,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 45925-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3580,14 +3566,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44538</v>
+        <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3599,8 +3585,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3633,49 +3624,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 45925-2023 artfynd.xlsx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 45925-2023 karta.png", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 45925-2023 georefererad karta.tif", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 45925-2023 FSC-klagomål.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 45925-2023 FSC-klagomål mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 45925-2023 tillsynsbegäran.docx", "A 45925-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 45925-2023 tillsynsbegäran mail.docx", "A 45925-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3685,14 +3676,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45530</v>
+        <v>45253</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3705,13 +3696,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>16.6</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3720,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3729,58 +3720,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3794,10 +3785,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45253</v>
+        <v>45471</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3810,13 +3801,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3843,49 +3834,53 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3895,14 +3890,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45855</v>
+        <v>44706</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3915,19 +3910,19 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3942,55 +3937,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4004,10 +3999,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44706</v>
+        <v>46169</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4020,7 +4015,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4029,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4047,55 +4042,55 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4109,10 +4104,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46043</v>
+        <v>45351</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4125,7 +4120,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4169,38 +4164,38 @@
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4214,10 +4209,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46169</v>
+        <v>45183</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4229,8 +4224,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4266,39 +4266,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44575</v>
+        <v>44783</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45407</v>
+        <v>45713</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45407</v>
+        <v>45433</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45203</v>
+        <v>45433</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45433</v>
+        <v>45265</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44783</v>
+        <v>45260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5259,7 +5259,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 45353-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45191</v>
+        <v>45576</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45433</v>
+        <v>44572</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 746-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44572</v>
+        <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5434,8 +5434,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5478,7 +5483,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 749-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5492,10 +5497,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45471</v>
+        <v>46029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5507,8 +5512,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5551,7 +5561,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5561,14 +5571,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45163</v>
+        <v>45825</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5581,7 +5591,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5624,7 +5634,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 3643-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5638,10 +5648,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45152</v>
+        <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5654,7 +5664,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5697,7 +5707,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5711,10 +5721,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45433</v>
+        <v>44886</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5727,7 +5737,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5770,7 +5780,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 5197-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45433</v>
+        <v>46049</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5799,8 +5809,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5843,7 +5858,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5857,10 +5872,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45282</v>
+        <v>46049</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5873,7 +5888,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5916,7 +5931,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5930,10 +5945,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45007</v>
+        <v>45575</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5946,7 +5961,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5989,7 +6004,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6003,10 +6018,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44664</v>
+        <v>45645</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6019,7 +6034,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6062,7 +6077,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6072,14 +6087,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44886</v>
+        <v>46059</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6091,8 +6106,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6135,7 +6155,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6149,10 +6169,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45446</v>
+        <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6165,7 +6185,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6208,7 +6228,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6222,10 +6242,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45265</v>
+        <v>45671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6238,7 +6258,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6281,7 +6301,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6295,10 +6315,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45163</v>
+        <v>46048</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6311,7 +6331,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6354,7 +6374,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6364,14 +6384,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44948</v>
+        <v>46008</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6383,8 +6403,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6427,7 +6452,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6437,14 +6462,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45104</v>
+        <v>46008</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6456,8 +6481,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6500,7 +6530,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6514,10 +6544,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45433</v>
+        <v>45671</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6530,7 +6560,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6573,7 +6603,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6587,10 +6617,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45259</v>
+        <v>45671</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6603,7 +6633,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6646,7 +6676,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6660,10 +6690,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45114</v>
+        <v>45940</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6676,7 +6706,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6719,7 +6749,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6733,10 +6763,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45611</v>
+        <v>45372</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6749,7 +6779,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6792,7 +6822,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6806,10 +6836,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44914</v>
+        <v>45152</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6821,13 +6851,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6870,7 +6895,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6884,10 +6909,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45784</v>
+        <v>46101</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6900,7 +6925,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6943,7 +6968,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6957,10 +6982,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45260</v>
+        <v>46101</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6973,7 +6998,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7016,7 +7041,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7026,14 +7051,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45090</v>
+        <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7045,13 +7070,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7094,7 +7114,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7108,10 +7128,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45713</v>
+        <v>45576</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7124,7 +7144,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7167,7 +7187,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45353-2024</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7181,10 +7201,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45576</v>
+        <v>45433</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7197,7 +7217,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7240,7 +7260,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7254,10 +7274,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45666</v>
+        <v>45799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7270,7 +7290,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7313,7 +7333,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7327,10 +7347,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44943</v>
+        <v>45014</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7343,7 +7363,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7386,7 +7406,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7400,10 +7420,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45446</v>
+        <v>45713</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7416,7 +7436,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7459,7 +7479,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7473,10 +7493,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45701</v>
+        <v>45825</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7489,7 +7509,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7532,7 +7552,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7546,10 +7566,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45575</v>
+        <v>46001</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7562,7 +7582,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7605,7 +7625,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7619,10 +7639,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44477</v>
+        <v>45827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7635,7 +7655,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7678,7 +7698,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7692,10 +7712,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45713</v>
+        <v>45755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7708,7 +7728,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7751,7 +7771,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7765,10 +7785,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45645</v>
+        <v>45845</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7781,7 +7801,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7824,7 +7844,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7838,10 +7858,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45014</v>
+        <v>45671</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7854,7 +7874,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7897,7 +7917,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7907,14 +7927,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45713</v>
+        <v>45848</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7927,7 +7947,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7970,7 +7990,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7984,10 +8004,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45713</v>
+        <v>44477</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8000,7 +8020,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8043,7 +8063,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8053,14 +8073,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45385</v>
+        <v>46148</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8072,13 +8092,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8121,7 +8136,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8131,14 +8146,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44977</v>
+        <v>45701</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8151,7 +8166,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8194,7 +8209,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8204,14 +8219,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45666</v>
+        <v>45104</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8224,7 +8239,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8267,7 +8282,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8277,14 +8292,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45140</v>
+        <v>45905</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8297,7 +8312,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8340,7 +8355,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8354,10 +8369,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44713</v>
+        <v>45114</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8370,7 +8385,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8413,7 +8428,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8427,10 +8442,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45187</v>
+        <v>44664</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8442,13 +8457,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8491,7 +8501,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8505,10 +8515,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44600</v>
+        <v>46184</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8521,7 +8531,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8564,7 +8574,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8574,14 +8584,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45217</v>
+        <v>45407</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8594,7 +8604,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8637,7 +8647,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8647,14 +8657,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45755</v>
+        <v>45140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8667,7 +8677,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8710,7 +8720,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8724,10 +8734,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45825</v>
+        <v>44623</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8740,7 +8750,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8783,7 +8793,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8797,10 +8807,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45827</v>
+        <v>45433</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8813,7 +8823,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8856,7 +8866,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8870,10 +8880,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45372</v>
+        <v>45446</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8886,7 +8896,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8929,7 +8939,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8943,10 +8953,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44623</v>
+        <v>45187</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8958,8 +8968,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9002,7 +9017,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9016,10 +9031,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45210</v>
+        <v>45259</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9032,7 +9047,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9075,7 +9090,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9089,10 +9104,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45845</v>
+        <v>46211</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9104,8 +9119,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9148,7 +9168,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9162,10 +9182,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45029</v>
+        <v>45191</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9178,7 +9198,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9221,7 +9241,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9231,14 +9251,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45671</v>
+        <v>45217</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9251,7 +9271,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9294,7 +9314,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9304,14 +9324,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45848</v>
+        <v>45236</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9323,8 +9343,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9367,7 +9392,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9381,10 +9406,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45576</v>
+        <v>45471</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9397,7 +9422,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9440,7 +9465,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9454,10 +9479,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45104</v>
+        <v>45163</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9470,7 +9495,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9513,7 +9538,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,10 +9552,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45189</v>
+        <v>45385</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9544,11 +9569,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9591,7 +9616,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9605,10 +9630,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45236</v>
+        <v>44914</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9622,11 +9647,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9669,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9683,10 +9708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45940</v>
+        <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9699,7 +9724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9742,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9752,14 +9777,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45825</v>
+        <v>46285</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9772,7 +9797,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9815,7 +9840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9829,10 +9854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45895</v>
+        <v>45007</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9845,7 +9870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9888,7 +9913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9902,10 +9927,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45671</v>
+        <v>46286</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9917,8 +9942,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9961,7 +9991,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9975,10 +10005,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45671</v>
+        <v>44575</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9991,7 +10021,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10034,7 +10064,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10048,10 +10078,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45671</v>
+        <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10064,7 +10094,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10107,7 +10137,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10121,10 +10151,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46001</v>
+        <v>46287</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10136,8 +10166,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10180,7 +10215,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 746-2026</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10194,10 +10229,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46029</v>
+        <v>45029</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10209,13 +10244,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10258,7 +10288,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 749-2026</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10272,10 +10302,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46029</v>
+        <v>45104</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10287,13 +10317,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10336,7 +10361,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3643-2026</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10350,10 +10375,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46043</v>
+        <v>44600</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10409,7 +10434,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 5197-2026</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10423,10 +10448,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46049</v>
+        <v>45210</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10438,13 +10463,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10487,7 +10507,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10501,10 +10521,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46049</v>
+        <v>45666</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10517,7 +10537,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10560,7 +10580,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10570,14 +10590,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46059</v>
+        <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10589,13 +10609,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10638,7 +10653,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10652,10 +10667,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46048</v>
+        <v>44713</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10668,7 +10683,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10711,7 +10726,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10725,10 +10740,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46008</v>
+        <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10746,7 +10761,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10789,7 +10804,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10803,10 +10818,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46008</v>
+        <v>45433</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10818,13 +10833,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10867,7 +10877,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10877,14 +10887,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46101</v>
+        <v>44977</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10897,7 +10907,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10940,7 +10950,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10954,10 +10964,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46101</v>
+        <v>45666</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10970,7 +10980,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11013,7 +11023,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11027,10 +11037,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45799</v>
+        <v>45407</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11043,7 +11053,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11086,7 +11096,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11100,10 +11110,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46148</v>
+        <v>44948</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11116,7 +11126,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11159,7 +11169,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11173,10 +11183,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45905</v>
+        <v>45446</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11189,7 +11199,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11232,7 +11242,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11246,10 +11256,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46184</v>
+        <v>44943</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11262,7 +11272,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11305,7 +11315,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11315,14 +11325,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46211</v>
+        <v>45090</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11336,11 +11346,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11383,7 +11393,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11397,10 +11407,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46287</v>
+        <v>45611</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11412,13 +11422,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11461,7 +11466,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11475,10 +11480,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46286</v>
+        <v>45784</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11490,13 +11495,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11549,14 +11549,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46285</v>
+        <v>45713</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30451-2025</t>
+          <t>A 22337-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45827</v>
+        <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>12.6</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1459,21 +1459,129 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Kransrams
+Myskmadra
+Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 30451-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Bokstumpbagge
 Gråbandad trägnagare
@@ -1481,107 +1589,215 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 30451-2025 artfynd.xlsx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 30451-2025 karta.png", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 30451-2025 georefererad karta.tif", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 30451-2025 FSC-klagomål.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 30451-2025 FSC-klagomål mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 30451-2025 tillsynsbegäran.docx", "A 30451-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 30451-2025 tillsynsbegäran mail.docx", "A 30451-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 60543-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Trollfibbla
+Kransrams
+Stor häxört
+Tvåblad</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 56294-2022</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>44887</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Crunoecia irrorata
 Skugglosta
@@ -1589,248 +1805,32 @@
 Strävlosta</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 56294-2022 artfynd.xlsx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 56294-2022 karta.png", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 56294-2022 georefererad karta.tif", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 56294-2022 FSC-klagomål.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 56294-2022 FSC-klagomål mail.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 56294-2022 tillsynsbegäran.docx", "A 56294-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 56294-2022 tillsynsbegäran mail.docx", "A 56294-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 22337-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45446</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Kransrams
-Myskmadra
-Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 22337-2024 artfynd.xlsx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 22337-2024 karta.png", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 22337-2024 georefererad karta.tif", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 22337-2024 FSC-klagomål.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 22337-2024 FSC-klagomål mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 22337-2024 tillsynsbegäran.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 22337-2024 tillsynsbegäran mail.docx", "A 22337-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 60543-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Trollfibbla
-Kransrams
-Stor häxört
-Tvåblad</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 60543-2023 artfynd.xlsx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 60543-2023 karta.png", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 60543-2023 georefererad karta.tif", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 60543-2023 FSC-klagomål.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 60543-2023 FSC-klagomål mail.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 60543-2023 tillsynsbegäran.docx", "A 60543-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 60543-2023 tillsynsbegäran mail.docx", "A 60543-2023")</f>
         <v/>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5166-2026</t>
+          <t>A 26736-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46049</v>
+        <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,25 +2196,20 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2229,159 +2224,164 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fläcklungört
+Månviol</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5166-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SJÖBO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Entita
 Blomkålssvamp</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 5166-2026 artfynd.xlsx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 5166-2026 karta.png", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 5166-2026 georefererad karta.tif", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 5166-2026 FSC-klagomål.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 5166-2026 FSC-klagomål mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 5166-2026 tillsynsbegäran.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 5166-2026 tillsynsbegäran mail.docx", "A 5166-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 5166-2026 prioriterade fågelarter.docx", "A 5166-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26736-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45090</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SJÖBO</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Fläcklungört
-Månviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 26736-2023 artfynd.xlsx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 26736-2023 karta.png", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 26736-2023 georefererad karta.tif", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 26736-2023 FSC-klagomål.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 26736-2023 FSC-klagomål mail.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 26736-2023 tillsynsbegäran.docx", "A 26736-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 26736-2023 tillsynsbegäran mail.docx", "A 26736-2023")</f>
         <v/>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47943-2023</t>
+          <t>A 27230-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45204</v>
+        <v>45471</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2980,10 +2980,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,46 +2992,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31678-2025</t>
+          <t>A 8150-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3045,10 +3049,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45834</v>
+        <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,10 +3065,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3097,46 +3101,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hedblomster</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35258-2024</t>
+          <t>A 31678-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3146,14 +3150,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45530</v>
+        <v>45834</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,10 +3170,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>16.6</v>
+        <v>3.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3178,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3199,49 +3203,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 31678-2025 artfynd.xlsx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 31678-2025 karta.png", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 31678-2025 georefererad karta.tif", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 31678-2025 FSC-klagomål.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 31678-2025 FSC-klagomål mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 31678-2025 tillsynsbegäran.docx", "A 31678-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 31678-2025 tillsynsbegäran mail.docx", "A 31678-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35454-2025</t>
+          <t>A 35258-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,10 +3259,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45855</v>
+        <v>45530</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,22 +3275,22 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>16.6</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3304,49 +3308,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35258-2024 artfynd.xlsx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35258-2024 karta.png", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35258-2024 georefererad karta.tif", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35258-2024 FSC-klagomål.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35258-2024 FSC-klagomål mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35258-2024 tillsynsbegäran.docx", "A 35258-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35258-2024 tillsynsbegäran mail.docx", "A 35258-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 71055-2021</t>
+          <t>A 35454-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3356,14 +3360,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44538</v>
+        <v>45855</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3376,10 +3380,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3388,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3409,49 +3413,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 35454-2025 artfynd.xlsx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 35454-2025 karta.png", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 35454-2025 georefererad karta.tif", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 35454-2025 FSC-klagomål.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 35454-2025 FSC-klagomål mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 35454-2025 tillsynsbegäran.docx", "A 35454-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 35454-2025 tillsynsbegäran mail.docx", "A 35454-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3765-2026</t>
+          <t>A 21425-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3465,10 +3469,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46043</v>
+        <v>44706</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3481,7 +3485,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3490,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3508,48 +3512,48 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
         <v/>
       </c>
     </row>
@@ -3573,7 +3577,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3670,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59610-2023</t>
+          <t>A 47943-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3680,10 +3684,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45253</v>
+        <v>45204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3696,20 +3700,20 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
@@ -3720,58 +3724,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Hedblomster</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 47943-2023 artfynd.xlsx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 47943-2023 karta.png", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 47943-2023 georefererad karta.tif", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 47943-2023 FSC-klagomål.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 47943-2023 FSC-klagomål mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 47943-2023 tillsynsbegäran.docx", "A 47943-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 47943-2023 tillsynsbegäran mail.docx", "A 47943-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27230-2024</t>
+          <t>A 3765-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3785,10 +3789,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45471</v>
+        <v>46043</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3801,20 +3805,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -3825,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3837,50 +3841,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fläcklungört</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 27230-2024 artfynd.xlsx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 3765-2026 artfynd.xlsx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 27230-2024 karta.png", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 3765-2026 karta.png", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 27230-2024 georefererad karta.tif", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 3765-2026 georefererad karta.tif", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 27230-2024 FSC-klagomål.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 3765-2026 FSC-klagomål.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 27230-2024 FSC-klagomål mail.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 3765-2026 FSC-klagomål mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 27230-2024 tillsynsbegäran.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 3765-2026 tillsynsbegäran.docx", "A 3765-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 27230-2024 tillsynsbegäran mail.docx", "A 27230-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/fåglar/A 27230-2024 prioriterade fågelarter.docx", "A 27230-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 3765-2026 tillsynsbegäran mail.docx", "A 3765-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21425-2022</t>
+          <t>A 24421-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44706</v>
+        <v>46169</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3919,10 +3919,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3937,55 +3937,55 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 21425-2022 artfynd.xlsx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 21425-2022 karta.png", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 21425-2022 georefererad karta.tif", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 21425-2022 FSC-klagomål.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 21425-2022 FSC-klagomål mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 21425-2022 tillsynsbegäran.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 21425-2022 tillsynsbegäran mail.docx", "A 21425-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 24421-2026</t>
+          <t>A 43335-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46169</v>
+        <v>45183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4014,8 +4014,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4051,46 +4056,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 24421-2026 artfynd.xlsx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 24421-2026 karta.png", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 24421-2026 georefererad karta.tif", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 24421-2026 FSC-klagomål.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 24421-2026 FSC-klagomål mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 24421-2026 tillsynsbegäran.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 24421-2026 tillsynsbegäran mail.docx", "A 24421-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8150-2024</t>
+          <t>A 71055-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45351</v>
+        <v>44538</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4120,7 +4125,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>7.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4132,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4153,49 +4158,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Fläcklungört</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 8150-2024 artfynd.xlsx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 71055-2021 artfynd.xlsx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 8150-2024 karta.png", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 71055-2021 karta.png", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 8150-2024 georefererad karta.tif", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 71055-2021 georefererad karta.tif", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 8150-2024 FSC-klagomål.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 71055-2021 FSC-klagomål.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 8150-2024 FSC-klagomål mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 71055-2021 FSC-klagomål mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 8150-2024 tillsynsbegäran.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 71055-2021 tillsynsbegäran.docx", "A 71055-2021")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 8150-2024 tillsynsbegäran mail.docx", "A 8150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 71055-2021 tillsynsbegäran mail.docx", "A 71055-2021")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43335-2023</t>
+          <t>A 59610-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4209,10 +4214,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45183</v>
+        <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4224,25 +4229,20 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4254,51 +4254,51 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 43335-2023 artfynd.xlsx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/artfynd/A 59610-2023 artfynd.xlsx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 43335-2023 karta.png", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor/A 59610-2023 karta.png", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 43335-2023 georefererad karta.tif", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/kartor_geotiff/A 59610-2023 georefererad karta.tif", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 43335-2023 FSC-klagomål.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomål/A 59610-2023 FSC-klagomål.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 43335-2023 FSC-klagomål mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/klagomålsmail/A 59610-2023 FSC-klagomål mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 43335-2023 tillsynsbegäran.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsyn/A 59610-2023 tillsynsbegäran.docx", "A 59610-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 43335-2023 tillsynsbegäran mail.docx", "A 43335-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1265/tillsynsmail/A 59610-2023 tillsynsbegäran mail.docx", "A 59610-2023")</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32732-2022</t>
+          <t>A 54959-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44783</v>
+        <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8858-2025</t>
+          <t>A 61875-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45713</v>
+        <v>45265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19883-2024</t>
+          <t>A 3258-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45433</v>
+        <v>44948</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19888-2024</t>
+          <t>A 8861-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45433</v>
+        <v>45713</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61875-2023</t>
+          <t>A 2449-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45265</v>
+        <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 60778-2023</t>
+          <t>A 29816-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45260</v>
+        <v>45825</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5276,7 +5276,7 @@
         <v>45576</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1235-2022</t>
+          <t>A 22330-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44572</v>
+        <v>45446</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5422,7 +5422,7 @@
         <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>46029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29816-2025</t>
+          <t>A 56137-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45825</v>
+        <v>44477</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54959-2022</t>
+          <t>A 1846-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44886</v>
+        <v>45671</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5797,7 +5797,7 @@
         <v>46049</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5404-2026</t>
+          <t>A 44893-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46049</v>
+        <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5931,7 +5931,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 44893-2024</t>
+          <t>A 5404-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45575</v>
+        <v>46049</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60947-2024</t>
+          <t>A 43745-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45645</v>
+        <v>45187</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6033,8 +6033,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6077,7 +6082,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7474-2026</t>
+          <t>A 8859-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6087,14 +6092,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46059</v>
+        <v>45713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6106,13 +6111,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8859-2025</t>
+          <t>A 60947-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45713</v>
+        <v>45645</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1846-2025</t>
+          <t>A 7474-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6238,14 +6238,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45671</v>
+        <v>46059</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6257,8 +6257,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6301,7 +6306,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4663-2026</t>
+          <t>A 1865-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6315,10 +6320,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46048</v>
+        <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6331,7 +6336,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6374,7 +6379,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62798-2025</t>
+          <t>A 1858-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6388,10 +6393,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46008</v>
+        <v>45671</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6403,13 +6408,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62807-2025</t>
+          <t>A 16429-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46008</v>
+        <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6481,13 +6481,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6530,7 +6525,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1858-2025</t>
+          <t>A 45348-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6544,10 +6539,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45671</v>
+        <v>45576</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6603,7 +6598,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1865-2025</t>
+          <t>A 4663-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6617,10 +6612,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45671</v>
+        <v>46048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6633,7 +6628,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6676,7 +6671,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49897-2025</t>
+          <t>A 28919-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6690,10 +6685,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45940</v>
+        <v>45104</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6706,7 +6701,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6749,7 +6744,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11500-2024</t>
+          <t>A 49897-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6763,10 +6758,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45372</v>
+        <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6779,7 +6774,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6822,7 +6817,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36414-2023</t>
+          <t>A 45981-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6836,10 +6831,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45152</v>
+        <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6851,8 +6846,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6895,7 +6895,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14573-2026</t>
+          <t>A 54711-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46101</v>
+        <v>45236</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6924,8 +6924,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14572-2026</t>
+          <t>A 62807-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46101</v>
+        <v>46008</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6997,8 +7002,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7041,7 +7051,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40463-2025</t>
+          <t>A 62798-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7055,10 +7065,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45895</v>
+        <v>46008</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7070,8 +7080,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7114,7 +7129,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45348-2024</t>
+          <t>A 2026-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7128,10 +7143,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45576</v>
+        <v>44575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7144,7 +7159,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7187,7 +7202,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19880-2024</t>
+          <t>A 40463-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7201,10 +7216,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45433</v>
+        <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7217,7 +7232,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7260,7 +7275,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24833-2025</t>
+          <t>A 14572-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7274,10 +7289,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45799</v>
+        <v>46101</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7290,7 +7305,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7333,7 +7348,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14747-2023</t>
+          <t>A 14573-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7347,10 +7362,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45014</v>
+        <v>46101</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7363,7 +7378,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7406,7 +7421,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8862-2025</t>
+          <t>A 1235-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7420,10 +7435,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45713</v>
+        <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7436,7 +7451,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7479,7 +7494,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29821-2025</t>
+          <t>A 27237-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7493,10 +7508,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45825</v>
+        <v>45471</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7509,7 +7524,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7552,7 +7567,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61431-2025</t>
+          <t>A 16979-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7566,10 +7581,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46001</v>
+        <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7582,7 +7597,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7625,7 +7640,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30453-2025</t>
+          <t>A 29821-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7639,10 +7654,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45827</v>
+        <v>45825</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7655,7 +7670,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7698,7 +7713,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16979-2025</t>
+          <t>A 30453-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7712,10 +7727,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45755</v>
+        <v>45827</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7728,7 +7743,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7771,7 +7786,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34173-2025</t>
+          <t>A 19883-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7785,10 +7800,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45845</v>
+        <v>45433</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7801,7 +7816,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7844,7 +7859,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1879-2025</t>
+          <t>A 19888-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7858,10 +7873,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45671</v>
+        <v>45433</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7874,7 +7889,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7917,7 +7932,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34780-2025</t>
+          <t>A 61431-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7927,14 +7942,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45848</v>
+        <v>46001</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7947,7 +7962,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7990,7 +8005,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56137-2021</t>
+          <t>A 28923-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8000,14 +8015,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44477</v>
+        <v>45104</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8020,7 +8035,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8063,7 +8078,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21479-2026</t>
+          <t>A 19884-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8073,14 +8088,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46148</v>
+        <v>45433</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8093,7 +8108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8136,7 +8151,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7059-2025</t>
+          <t>A 34173-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8150,10 +8165,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45701</v>
+        <v>45845</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8166,7 +8181,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8209,7 +8224,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28923-2023</t>
+          <t>A 60371-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8219,14 +8234,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45104</v>
+        <v>45259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8239,7 +8254,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8282,7 +8297,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42599-2025</t>
+          <t>A 61031-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8296,10 +8311,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45905</v>
+        <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8311,8 +8326,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>9.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8355,7 +8375,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31403-2023</t>
+          <t>A 1879-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8369,10 +8389,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45114</v>
+        <v>45671</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8385,7 +8405,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8428,7 +8448,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15856-2022</t>
+          <t>A 24833-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8442,10 +8462,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44664</v>
+        <v>45799</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8458,7 +8478,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8501,7 +8521,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26781-2026</t>
+          <t>A 34780-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8511,14 +8531,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46184</v>
+        <v>45848</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8531,7 +8551,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8574,7 +8594,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16346-2024</t>
+          <t>A 60778-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8588,10 +8608,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45407</v>
+        <v>45260</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8604,7 +8624,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8647,7 +8667,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34776-2023</t>
+          <t>A 1031-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8657,14 +8677,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45140</v>
+        <v>45666</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8677,7 +8697,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8720,7 +8740,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10454-2022</t>
+          <t>A 7059-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8734,10 +8754,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44623</v>
+        <v>45701</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8750,7 +8770,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8793,7 +8813,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19884-2024</t>
+          <t>A 8858-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8807,10 +8827,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45433</v>
+        <v>45713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8823,7 +8843,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8866,7 +8886,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22425-2024</t>
+          <t>A 8862-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8880,10 +8900,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45446</v>
+        <v>45713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8896,7 +8916,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8939,7 +8959,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43745-2023</t>
+          <t>A 12965-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8953,10 +8973,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45187</v>
+        <v>45385</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8970,11 +8990,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9017,7 +9037,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60371-2023</t>
+          <t>A 8568-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9027,14 +9047,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45259</v>
+        <v>44977</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9047,7 +9067,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9090,7 +9110,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30704-2026</t>
+          <t>A 21479-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9100,14 +9120,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46211</v>
+        <v>46148</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9119,13 +9139,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9168,7 +9183,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46397-2023</t>
+          <t>A 34776-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9178,14 +9193,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45191</v>
+        <v>45140</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9198,7 +9213,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9241,7 +9256,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50798-2023</t>
+          <t>A 22406-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9251,14 +9266,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45217</v>
+        <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9271,7 +9286,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9314,7 +9329,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54711-2023</t>
+          <t>A 6229-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9328,10 +9343,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45236</v>
+        <v>44600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9343,13 +9358,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9392,7 +9402,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 27237-2024</t>
+          <t>A 11500-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9406,10 +9416,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45471</v>
+        <v>45372</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9422,7 +9432,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9465,7 +9475,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 39414-2023</t>
+          <t>A 10454-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9479,10 +9489,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45163</v>
+        <v>44623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9495,7 +9505,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9538,7 +9548,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 12965-2024</t>
+          <t>A 42599-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9552,10 +9562,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45385</v>
+        <v>45905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9567,13 +9577,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9616,7 +9621,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61031-2022</t>
+          <t>A 16373-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9630,10 +9635,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44914</v>
+        <v>45407</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9645,13 +9650,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 47656-2023</t>
+          <t>A 16346-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45203</v>
+        <v>45407</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9767,7 +9767,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38725-2026</t>
+          <t>A 47656-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9777,14 +9777,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46285</v>
+        <v>45203</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 13754-2023</t>
+          <t>A 26781-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45007</v>
+        <v>46184</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9913,7 +9913,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38944-2026</t>
+          <t>A 19880-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46286</v>
+        <v>45433</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9942,13 +9942,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9991,7 +9986,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2026-2022</t>
+          <t>A 32732-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10005,10 +10000,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44575</v>
+        <v>44783</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10021,7 +10016,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10064,7 +10059,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64905-2023</t>
+          <t>A 46397-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10078,10 +10073,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45282</v>
+        <v>45191</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10094,7 +10089,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10137,7 +10132,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38990-2026</t>
+          <t>A 39407-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10147,14 +10142,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46287</v>
+        <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10166,13 +10161,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10215,7 +10205,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16429-2023</t>
+          <t>A 36414-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10229,10 +10219,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45029</v>
+        <v>45152</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10245,7 +10235,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10288,7 +10278,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28919-2023</t>
+          <t>A 64905-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10302,10 +10292,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45104</v>
+        <v>45282</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10318,7 +10308,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10361,7 +10351,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6229-2022</t>
+          <t>A 30704-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10375,10 +10365,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44600</v>
+        <v>46211</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10390,8 +10380,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10434,7 +10429,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 49298-2023</t>
+          <t>A 15856-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10448,10 +10443,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45210</v>
+        <v>44664</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10464,7 +10459,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10507,7 +10502,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1098-2025</t>
+          <t>A 22425-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10521,10 +10516,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45666</v>
+        <v>45446</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10537,7 +10532,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10580,7 +10575,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 39407-2023</t>
+          <t>A 39414-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10590,14 +10585,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10610,7 +10605,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>9.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10653,7 +10648,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22406-2022</t>
+          <t>A 31403-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10667,10 +10662,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44713</v>
+        <v>45114</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10683,7 +10678,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10726,7 +10721,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 45981-2023</t>
+          <t>A 26730-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10736,14 +10731,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45189</v>
+        <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10761,7 +10756,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10804,7 +10799,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19877-2024</t>
+          <t>A 38990-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10818,10 +10813,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45433</v>
+        <v>46287</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10833,8 +10828,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10877,7 +10877,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8568-2023</t>
+          <t>A 38944-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10887,14 +10887,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44977</v>
+        <v>46286</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10906,8 +10906,13 @@
           <t>SJÖBO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10950,7 +10955,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1031-2025</t>
+          <t>A 38725-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10960,14 +10965,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45666</v>
+        <v>46285</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11023,7 +11028,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16373-2024</t>
+          <t>A 14747-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11037,10 +11042,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45407</v>
+        <v>45014</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11053,7 +11058,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11096,7 +11101,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 3258-2023</t>
+          <t>A 1098-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11106,14 +11111,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44948</v>
+        <v>45666</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11126,7 +11131,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11169,7 +11174,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22330-2024</t>
+          <t>A 50798-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11179,14 +11184,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45446</v>
+        <v>45217</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11199,7 +11204,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11242,7 +11247,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2449-2023</t>
+          <t>A 49298-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11256,10 +11261,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44943</v>
+        <v>45210</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11272,7 +11277,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11315,7 +11320,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26730-2023</t>
+          <t>A 19877-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11325,14 +11330,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45090</v>
+        <v>45433</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11344,13 +11349,8 @@
           <t>SJÖBO</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11393,7 +11393,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52959-2024</t>
+          <t>A 13754-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45611</v>
+        <v>45007</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11466,7 +11466,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21973-2025</t>
+          <t>A 52959-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45784</v>
+        <v>45611</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8861-2025</t>
+          <t>A 21973-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11553,10 +11553,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45713</v>
+        <v>45784</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44544</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45758</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45446</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>45827</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>45259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44887</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45946</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44749</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45090</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>46049</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45407</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>46147</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>44643</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45471</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45834</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>45530</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>45855</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44706</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>45189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>45204</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>46043</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46169</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>44538</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44656</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>44844</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>44706</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44495</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45265</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>44948</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45713</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44943</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45825</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>45576</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>45446</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>46029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44477</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46043</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45671</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46049</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>46049</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45187</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45713</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45645</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46059</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>45671</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45029</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>45576</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>46048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45104</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45940</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45236</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>46008</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>46008</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>46101</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>46101</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>45471</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45825</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45827</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45433</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45433</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>46001</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45104</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45433</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45845</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>44914</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45671</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45799</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45848</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45260</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>45666</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45701</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45713</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45713</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45385</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44977</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>46148</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45140</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>44713</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>45372</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>45905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45407</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45407</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45203</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>46184</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>45433</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44783</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45191</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>45152</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>45282</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>46211</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>44664</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45446</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45114</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>46287</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>46286</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>46285</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>45014</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>45666</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45217</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45210</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>45433</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45007</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45611</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45784</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46003</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>

--- a/Översikt SJÖBO.xlsx
+++ b/Översikt SJÖBO.xlsx
@@ -601,7 +601,7 @@
         <v>44867</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>44575</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>44544</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>44574</v>
       </c>
       <c r="E5